--- a/results/synapse_table.xlsx
+++ b/results/synapse_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB53"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,64 +585,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>94.54665808316267</v>
+        <v>84.5608327264332</v>
       </c>
       <c r="G2" t="n">
-        <v>10.97180677436661</v>
+        <v>10.37623227202582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08712792302785673</v>
+        <v>0.07737796324921047</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5515287480459286</v>
+        <v>0.6253241477476021</v>
       </c>
       <c r="J2" t="n">
-        <v>97.72223793850586</v>
+        <v>83.62755543676845</v>
       </c>
       <c r="K2" t="n">
-        <v>14.15453762081717</v>
+        <v>14.03104424429663</v>
       </c>
       <c r="L2" t="n">
-        <v>10.44482652189057</v>
+        <v>12.86208212821971</v>
       </c>
       <c r="M2" t="n">
-        <v>1085.147617405433</v>
+        <v>1092.828360628839</v>
       </c>
       <c r="N2" t="n">
-        <v>1552.229473400429</v>
+        <v>1592.834996083847</v>
       </c>
       <c r="O2" t="n">
-        <v>799.7130187234761</v>
+        <v>1285.802319252512</v>
       </c>
       <c r="P2" t="n">
-        <v>89.30091857910156</v>
+        <v>88.45500946044922</v>
       </c>
       <c r="Q2" t="n">
-        <v>227.1483154296875</v>
+        <v>204.0211181640625</v>
       </c>
       <c r="R2" t="n">
-        <v>8.529748283752861</v>
+        <v>7.780205655526992</v>
       </c>
       <c r="S2" t="n">
-        <v>9.455966949462891</v>
+        <v>9.800426483154297</v>
       </c>
       <c r="T2" t="n">
-        <v>17.14501190185547</v>
+        <v>15.67255401611328</v>
       </c>
       <c r="U2" t="n">
-        <v>16.13150024414062</v>
+        <v>15.13949584960938</v>
       </c>
       <c r="V2" t="n">
         <v>34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.554364042042096</v>
+        <v>1.458778638510444</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -654,10 +654,10 @@
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -675,64 +675,64 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>23.32143432982485</v>
+        <v>34.92478816276656</v>
       </c>
       <c r="G3" t="n">
-        <v>5.449199246556983</v>
+        <v>6.668404710298625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02149148554146573</v>
+        <v>0.03195816417380496</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3059714643799421</v>
+        <v>0.3860645935959985</v>
       </c>
       <c r="J3" t="n">
-        <v>21.92953613081337</v>
+        <v>31.90394581328354</v>
       </c>
       <c r="K3" t="n">
-        <v>6.552406975486628</v>
+        <v>9.536226166289516</v>
       </c>
       <c r="L3" t="n">
-        <v>4.905668442255195</v>
+        <v>5.956241320297747</v>
       </c>
       <c r="M3" t="n">
-        <v>1085.147617405433</v>
+        <v>1092.828360628839</v>
       </c>
       <c r="N3" t="n">
-        <v>1552.229473400429</v>
+        <v>1592.834996083847</v>
       </c>
       <c r="O3" t="n">
-        <v>438.8927364825122</v>
+        <v>613.9084241064048</v>
       </c>
       <c r="P3" t="n">
-        <v>88.94581604003906</v>
+        <v>63.61301422119141</v>
       </c>
       <c r="Q3" t="n">
-        <v>227.1483154296875</v>
+        <v>204.0211181640625</v>
       </c>
       <c r="R3" t="n">
-        <v>10.36945812807882</v>
+        <v>11.39383561643836</v>
       </c>
       <c r="S3" t="n">
-        <v>6.040370941162109</v>
+        <v>5.980472564697266</v>
       </c>
       <c r="T3" t="n">
-        <v>19.74161529541016</v>
+        <v>15.49085998535156</v>
       </c>
       <c r="U3" t="n">
-        <v>18.87944412231445</v>
+        <v>14.75030136108398</v>
       </c>
       <c r="V3" t="n">
         <v>34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81914444616691</v>
+        <v>1.421277481818923</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -744,16 +744,16 @@
         <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4_stack4</t>
+          <t>4_stack2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -765,64 +765,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>216.5882675852777</v>
+        <v>52.20913307181591</v>
       </c>
       <c r="G4" t="n">
-        <v>16.60628637640747</v>
+        <v>8.153203837963112</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07051641926981747</v>
+        <v>0.02701226426312793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5959153571003211</v>
+        <v>1.226646619458725</v>
       </c>
       <c r="J4" t="n">
-        <v>204.597246713559</v>
+        <v>42.2526198377775</v>
       </c>
       <c r="K4" t="n">
-        <v>14.45613222419539</v>
+        <v>7.399741764770707</v>
       </c>
       <c r="L4" t="n">
-        <v>11.73061927655518</v>
+        <v>7.099908920263616</v>
       </c>
       <c r="M4" t="n">
-        <v>3071.458673426744</v>
+        <v>1932.793658585742</v>
       </c>
       <c r="N4" t="n">
-        <v>4142.979517769711</v>
+        <v>2400.394492620544</v>
       </c>
       <c r="O4" t="n">
-        <v>615.1638605565201</v>
+        <v>118.2071882561732</v>
       </c>
       <c r="P4" t="n">
-        <v>71.32909393310547</v>
+        <v>70.91806030273438</v>
       </c>
       <c r="Q4" t="n">
-        <v>440.7059020996094</v>
+        <v>107.1266098022461</v>
       </c>
       <c r="R4" t="n">
-        <v>9.046649703138252</v>
+        <v>8.061872909698996</v>
       </c>
       <c r="S4" t="n">
-        <v>17.36882400512695</v>
+        <v>19.00606918334961</v>
       </c>
       <c r="T4" t="n">
-        <v>29.14646148681641</v>
+        <v>15.49433135986328</v>
       </c>
       <c r="U4" t="n">
-        <v>24.2186279296875</v>
+        <v>16.54124450683594</v>
       </c>
       <c r="V4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.333605915864901</v>
+        <v>1.593845289212394</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -831,7 +831,7 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
         <v>2</v>
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4_stack4</t>
+          <t>4_stack2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,64 +855,64 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>196.1200522159563</v>
+        <v>24.29279287717144</v>
       </c>
       <c r="G5" t="n">
-        <v>15.80214561370957</v>
+        <v>5.561523581112946</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1656016715832362</v>
+        <v>0.01256874616142257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9240604409785956</v>
+        <v>1.587181559021662</v>
       </c>
       <c r="J5" t="n">
-        <v>208.4883947663176</v>
+        <v>15.93860478784432</v>
       </c>
       <c r="K5" t="n">
-        <v>15.2438359504471</v>
+        <v>13.43429924579264</v>
       </c>
       <c r="L5" t="n">
-        <v>10.77465859425516</v>
+        <v>9.552122853461727</v>
       </c>
       <c r="M5" t="n">
-        <v>1184.287877899715</v>
+        <v>1932.793658585742</v>
       </c>
       <c r="N5" t="n">
-        <v>1432.884545861338</v>
+        <v>2400.394492620544</v>
       </c>
       <c r="O5" t="n">
-        <v>1234.133262852452</v>
+        <v>1410.129760202998</v>
       </c>
       <c r="P5" t="n">
-        <v>114.2143630981445</v>
+        <v>66.36683654785156</v>
       </c>
       <c r="Q5" t="n">
-        <v>256.3981018066406</v>
+        <v>107.1266098022461</v>
       </c>
       <c r="R5" t="n">
-        <v>6.812707182320442</v>
+        <v>8.457286432160805</v>
       </c>
       <c r="S5" t="n">
-        <v>13.45244598388672</v>
+        <v>26.67567443847656</v>
       </c>
       <c r="T5" t="n">
-        <v>14.5579719543457</v>
+        <v>16.80694580078125</v>
       </c>
       <c r="U5" t="n">
-        <v>14.34881591796875</v>
+        <v>17.08962249755859</v>
       </c>
       <c r="V5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.382592020036884</v>
+        <v>1.646684703856187</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
         <v>2</v>
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>6.279952029079215</v>
+        <v>165.1605929802871</v>
       </c>
       <c r="G6" t="n">
-        <v>2.827699287842235</v>
+        <v>14.50134470366146</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002044615505789255</v>
+        <v>0.1464911706149212</v>
       </c>
       <c r="I6" t="n">
-        <v>1.672615338286883</v>
+        <v>1.184387196221472</v>
       </c>
       <c r="J6" t="n">
-        <v>4.155685745819777</v>
+        <v>182.2559577863083</v>
       </c>
       <c r="K6" t="n">
-        <v>7.454668098799496</v>
+        <v>14.49553247207279</v>
       </c>
       <c r="L6" t="n">
-        <v>3.907547821321398</v>
+        <v>11.68787243690289</v>
       </c>
       <c r="M6" t="n">
-        <v>3071.458673426744</v>
+        <v>1127.444011041743</v>
       </c>
       <c r="N6" t="n">
-        <v>4142.979517769711</v>
+        <v>1216.63561732897</v>
       </c>
       <c r="O6" t="n">
-        <v>1234.133262852452</v>
+        <v>978.926571977442</v>
       </c>
       <c r="P6" t="n">
-        <v>62.65789413452148</v>
+        <v>129.6198272705078</v>
       </c>
       <c r="Q6" t="n">
-        <v>440.7059020996094</v>
+        <v>129.9382019042969</v>
       </c>
       <c r="R6" t="n">
-        <v>7.052631578947368</v>
+        <v>6.390368271954674</v>
       </c>
       <c r="S6" t="n">
-        <v>23.8155632019043</v>
+        <v>20.3828010559082</v>
       </c>
       <c r="T6" t="n">
-        <v>14.23851776123047</v>
+        <v>17.20957565307617</v>
       </c>
       <c r="U6" t="n">
-        <v>14.36063766479492</v>
+        <v>17.82429885864258</v>
       </c>
       <c r="V6" t="n">
         <v>31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.383731114225436</v>
+        <v>1.71747505199024</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1011,10 +1011,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
@@ -1023,7 +1023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1032,67 +1032,67 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>150.7050066099234</v>
+        <v>102.6177982639215</v>
       </c>
       <c r="G7" t="n">
-        <v>13.85220466226689</v>
+        <v>11.43053099130921</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6636202318603845</v>
+        <v>0.06482144253333359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.527135479532622</v>
+        <v>0.9502608405183065</v>
       </c>
       <c r="J7" t="n">
-        <v>170.1209850066193</v>
+        <v>92.1352546703428</v>
       </c>
       <c r="K7" t="n">
-        <v>10.7186145112743</v>
+        <v>13.03827996704315</v>
       </c>
       <c r="L7" t="n">
-        <v>7.020160034046455</v>
+        <v>7.191178629248816</v>
       </c>
       <c r="M7" t="n">
-        <v>227.0952562543775</v>
+        <v>1583.084150142935</v>
       </c>
       <c r="N7" t="n">
-        <v>111.027661057076</v>
+        <v>1589.696404958558</v>
       </c>
       <c r="O7" t="n">
-        <v>1749.21529890134</v>
+        <v>681.9766191360962</v>
       </c>
       <c r="P7" t="n">
-        <v>133.8877258300781</v>
+        <v>61.66102981567383</v>
       </c>
       <c r="Q7" t="n">
-        <v>248.3955688476562</v>
+        <v>255.0967254638672</v>
       </c>
       <c r="R7" t="n">
-        <v>4.450261780104712</v>
+        <v>8.965342349957735</v>
       </c>
       <c r="S7" t="n">
-        <v>10.13739013671875</v>
+        <v>21.26969146728516</v>
       </c>
       <c r="T7" t="n">
-        <v>19.2310905456543</v>
+        <v>22.38300323486328</v>
       </c>
       <c r="U7" t="n">
-        <v>18.24848175048828</v>
+        <v>22.13632202148438</v>
       </c>
       <c r="V7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.758347545208834</v>
+        <v>2.132963608623924</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -1101,19 +1101,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1122,67 +1122,67 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>54.18951391256915</v>
+        <v>78.71812809334939</v>
       </c>
       <c r="G8" t="n">
-        <v>8.306397054286492</v>
+        <v>10.011345243072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03355373026969893</v>
+        <v>0.06302329860179971</v>
       </c>
       <c r="I8" t="n">
-        <v>1.563246253640858</v>
+        <v>0.5390552164821399</v>
       </c>
       <c r="J8" t="n">
-        <v>39.48430779539508</v>
+        <v>79.49304253137751</v>
       </c>
       <c r="K8" t="n">
-        <v>10.00270710789346</v>
+        <v>12.78572213935404</v>
       </c>
       <c r="L8" t="n">
-        <v>6.250817154817046</v>
+        <v>6.085695149005605</v>
       </c>
       <c r="M8" t="n">
-        <v>1615.007138610326</v>
+        <v>1249.032180792605</v>
       </c>
       <c r="N8" t="n">
-        <v>1940.080871707939</v>
+        <v>1754.237044701801</v>
       </c>
       <c r="O8" t="n">
-        <v>2424.404714729</v>
+        <v>681.9766191360962</v>
       </c>
       <c r="P8" t="n">
-        <v>60.0568733215332</v>
+        <v>94.58654022216797</v>
       </c>
       <c r="Q8" t="n">
-        <v>425.8230590820312</v>
+        <v>80.39250183105469</v>
       </c>
       <c r="R8" t="n">
-        <v>6.187203791469194</v>
+        <v>9.191239316239317</v>
       </c>
       <c r="S8" t="n">
-        <v>21.93129348754883</v>
+        <v>12.9010124206543</v>
       </c>
       <c r="T8" t="n">
-        <v>14.02932739257812</v>
+        <v>23.93263626098633</v>
       </c>
       <c r="U8" t="n">
-        <v>14.31143569946289</v>
+        <v>22.13205337524414</v>
       </c>
       <c r="V8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.378990218180278</v>
+        <v>2.132552299686528</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1191,19 +1191,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1212,67 +1212,67 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>18.01346476009329</v>
+        <v>34.50673131588045</v>
       </c>
       <c r="G9" t="n">
-        <v>4.789097584122094</v>
+        <v>6.628373470990467</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08291141320523858</v>
+        <v>0.04079112435338021</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6964964425463273</v>
+        <v>0.5966055059654756</v>
       </c>
       <c r="J9" t="n">
-        <v>19.00915175861062</v>
+        <v>19.39487448817508</v>
       </c>
       <c r="K9" t="n">
-        <v>3.310339018737079</v>
+        <v>10.23660256873005</v>
       </c>
       <c r="L9" t="n">
-        <v>3.221842082930575</v>
+        <v>6.080637040532735</v>
       </c>
       <c r="M9" t="n">
-        <v>217.2615815328443</v>
+        <v>845.9372440176685</v>
       </c>
       <c r="N9" t="n">
-        <v>138.3726362361509</v>
+        <v>805.7940390287224</v>
       </c>
       <c r="O9" t="n">
-        <v>602.6094960553667</v>
+        <v>681.9766191360962</v>
       </c>
       <c r="P9" t="n">
-        <v>83.20587921142578</v>
+        <v>68.32024383544922</v>
       </c>
       <c r="Q9" t="n">
-        <v>265.7477111816406</v>
+        <v>87.19190979003906</v>
       </c>
       <c r="R9" t="n">
-        <v>12.69117647058824</v>
+        <v>8.51963746223565</v>
       </c>
       <c r="S9" t="n">
-        <v>14.02007293701172</v>
+        <v>13.78517532348633</v>
       </c>
       <c r="T9" t="n">
-        <v>20.12942504882812</v>
+        <v>23.10601425170898</v>
       </c>
       <c r="U9" t="n">
-        <v>19.92119598388672</v>
+        <v>22.13089752197266</v>
       </c>
       <c r="V9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.919523308011859</v>
+        <v>2.132440926489003</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -1281,19 +1281,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,67 +1302,67 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>17.39468767106655</v>
+        <v>4.023872892926404</v>
       </c>
       <c r="G10" t="n">
-        <v>4.706124117691663</v>
+        <v>2.263482734694872</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01077065683191608</v>
+        <v>0.002541793430603857</v>
       </c>
       <c r="I10" t="n">
-        <v>2.372808631096043</v>
+        <v>1.299661801906902</v>
       </c>
       <c r="J10" t="n">
-        <v>13.73204234385857</v>
+        <v>3.00839780661885</v>
       </c>
       <c r="K10" t="n">
-        <v>9.531931477467648</v>
+        <v>6.633177918833388</v>
       </c>
       <c r="L10" t="n">
-        <v>2.835408247922682</v>
+        <v>1.735099402771775</v>
       </c>
       <c r="M10" t="n">
-        <v>1615.007138610326</v>
+        <v>1583.084150142935</v>
       </c>
       <c r="N10" t="n">
-        <v>1940.080871707939</v>
+        <v>1589.696404958558</v>
       </c>
       <c r="O10" t="n">
-        <v>274.6659558517983</v>
+        <v>978.926571977442</v>
       </c>
       <c r="P10" t="n">
-        <v>64.28358459472656</v>
+        <v>54.70370483398438</v>
       </c>
       <c r="Q10" t="n">
-        <v>425.8230590820312</v>
+        <v>255.0967254638672</v>
       </c>
       <c r="R10" t="n">
-        <v>8.126865671641792</v>
+        <v>6.481481481481482</v>
       </c>
       <c r="S10" t="n">
-        <v>25.85875701904297</v>
+        <v>23.09311676025391</v>
       </c>
       <c r="T10" t="n">
-        <v>10.89795303344727</v>
+        <v>17.76855850219727</v>
       </c>
       <c r="U10" t="n">
-        <v>11.95222473144531</v>
+        <v>17.82120895385742</v>
       </c>
       <c r="V10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.151666494981636</v>
+        <v>1.717177321660222</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1371,10 +1371,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1383,7 +1383,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1392,67 +1392,67 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>5.858191133407257</v>
+        <v>1.881226390774671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.731095130468915</v>
+        <v>1.547660115572446</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02696376916745241</v>
+        <v>0.001188330001664673</v>
       </c>
       <c r="I11" t="n">
-        <v>1.141387522865289</v>
+        <v>2.248884837781639</v>
       </c>
       <c r="J11" t="n">
-        <v>3.438044355089222</v>
+        <v>1.147287939200926</v>
       </c>
       <c r="K11" t="n">
-        <v>3.149893106113272</v>
+        <v>1.031330888391748</v>
       </c>
       <c r="L11" t="n">
-        <v>1.234643689210292</v>
+        <v>0.6450013958335229</v>
       </c>
       <c r="M11" t="n">
-        <v>217.2615815328443</v>
+        <v>1583.084150142935</v>
       </c>
       <c r="N11" t="n">
-        <v>138.3726362361509</v>
+        <v>1589.696404958558</v>
       </c>
       <c r="O11" t="n">
-        <v>1749.21529890134</v>
+        <v>423.2782456342025</v>
       </c>
       <c r="P11" t="n">
-        <v>99.5</v>
+        <v>82.18181610107422</v>
       </c>
       <c r="Q11" t="n">
-        <v>265.7477111816406</v>
+        <v>255.0967254638672</v>
       </c>
       <c r="R11" t="n">
-        <v>9.23076923076923</v>
+        <v>8.454545454545455</v>
       </c>
       <c r="S11" t="n">
-        <v>20.80833435058594</v>
+        <v>25.59999847412109</v>
       </c>
       <c r="T11" t="n">
-        <v>18.23073577880859</v>
+        <v>11.38341903686523</v>
       </c>
       <c r="U11" t="n">
-        <v>18.24734115600586</v>
+        <v>11.51303863525391</v>
       </c>
       <c r="V11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.758237642284544</v>
+        <v>1.109348355605063</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -1461,88 +1461,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5_stack1-4</t>
+          <t>4_stack5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>179.0328687403339</v>
+        <v>125.0273232618309</v>
       </c>
       <c r="G12" t="n">
-        <v>15.09807034980208</v>
+        <v>12.61704133897284</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1647574339772631</v>
+        <v>0.1652040569927973</v>
       </c>
       <c r="I12" t="n">
-        <v>1.785847350274784</v>
+        <v>0.8132080033893057</v>
       </c>
       <c r="J12" t="n">
-        <v>180.4703652018352</v>
+        <v>129.7086337890394</v>
       </c>
       <c r="K12" t="n">
-        <v>12.37562106573656</v>
+        <v>12.9276322477163</v>
       </c>
       <c r="L12" t="n">
-        <v>11.77222969596246</v>
+        <v>11.51463554650306</v>
       </c>
       <c r="M12" t="n">
-        <v>1086.645163246721</v>
+        <v>756.805405010616</v>
       </c>
       <c r="N12" t="n">
-        <v>1609.469529047875</v>
+        <v>709.8708477620967</v>
       </c>
       <c r="O12" t="n">
-        <v>2504.281858867589</v>
+        <v>1349.437254317734</v>
       </c>
       <c r="P12" t="n">
-        <v>78.3043212890625</v>
+        <v>85.76812744140625</v>
       </c>
       <c r="Q12" t="n">
-        <v>408.3299865722656</v>
+        <v>159.6872100830078</v>
       </c>
       <c r="R12" t="n">
-        <v>7.10065127294257</v>
+        <v>5.789662598707825</v>
       </c>
       <c r="S12" t="n">
-        <v>31.92845916748047</v>
+        <v>17.91007614135742</v>
       </c>
       <c r="T12" t="n">
-        <v>17.87860488891602</v>
+        <v>22.02397918701172</v>
       </c>
       <c r="U12" t="n">
-        <v>19.43573379516602</v>
+        <v>21.48800277709961</v>
       </c>
       <c r="V12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W12" t="n">
-        <v>1.872746197482874</v>
+        <v>2.070494271861424</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -1551,88 +1551,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5_stack2-4</t>
+          <t>4_stack5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>145.1330080791446</v>
+        <v>70.11060029461055</v>
       </c>
       <c r="G13" t="n">
-        <v>13.59371491288289</v>
+        <v>9.448152666009314</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2098786746287957</v>
+        <v>0.04371800109338758</v>
       </c>
       <c r="I13" t="n">
-        <v>1.363206042131974</v>
+        <v>1.604121207104173</v>
       </c>
       <c r="J13" t="n">
-        <v>139.2459237946164</v>
+        <v>52.62213510949175</v>
       </c>
       <c r="K13" t="n">
-        <v>14.29384311426795</v>
+        <v>11.42570779614305</v>
       </c>
       <c r="L13" t="n">
-        <v>10.14063002034302</v>
+        <v>9.941571652976142</v>
       </c>
       <c r="M13" t="n">
-        <v>691.5090746396019</v>
+        <v>1603.700959356417</v>
       </c>
       <c r="N13" t="n">
-        <v>592.6444692325761</v>
+        <v>1944.39643450521</v>
       </c>
       <c r="O13" t="n">
-        <v>1070.651897613995</v>
+        <v>2805.272747782743</v>
       </c>
       <c r="P13" t="n">
-        <v>66.1614990234375</v>
+        <v>61.00719451904297</v>
       </c>
       <c r="Q13" t="n">
-        <v>287.3195190429688</v>
+        <v>256.7391052246094</v>
       </c>
       <c r="R13" t="n">
-        <v>5.82192513368984</v>
+        <v>6.670863309352518</v>
       </c>
       <c r="S13" t="n">
-        <v>24.96876525878906</v>
+        <v>23.65461349487305</v>
       </c>
       <c r="T13" t="n">
-        <v>18.31620788574219</v>
+        <v>14.74615097045898</v>
       </c>
       <c r="U13" t="n">
-        <v>19.60207748413086</v>
+        <v>15.18851089477539</v>
       </c>
       <c r="V13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W13" t="n">
-        <v>1.888774381150509</v>
+        <v>1.463501523708478</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -1641,88 +1641,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AB13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5_stack2-4</t>
+          <t>4_stack5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>65.62003194738961</v>
+        <v>18.69172995199843</v>
       </c>
       <c r="G14" t="n">
-        <v>9.140569982347992</v>
+        <v>4.878426973358839</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08494763681583198</v>
+        <v>0.07529923076635954</v>
       </c>
       <c r="I14" t="n">
-        <v>1.22187052224366</v>
+        <v>0.5334264930008338</v>
       </c>
       <c r="J14" t="n">
-        <v>50.87490294675859</v>
+        <v>20.61386024780735</v>
       </c>
       <c r="K14" t="n">
-        <v>13.11226733871052</v>
+        <v>5.41505701591934</v>
       </c>
       <c r="L14" t="n">
-        <v>6.433640787450132</v>
+        <v>3.070913304007383</v>
       </c>
       <c r="M14" t="n">
-        <v>772.4762501593191</v>
+        <v>248.2326812872183</v>
       </c>
       <c r="N14" t="n">
-        <v>505.2739387823611</v>
+        <v>176.271124074008</v>
       </c>
       <c r="O14" t="n">
-        <v>1070.651897613995</v>
+        <v>144.8852128211243</v>
       </c>
       <c r="P14" t="n">
-        <v>60.81076431274414</v>
+        <v>49.12820434570312</v>
       </c>
       <c r="Q14" t="n">
-        <v>271.667236328125</v>
+        <v>220.4149932861328</v>
       </c>
       <c r="R14" t="n">
-        <v>5.741319444444445</v>
+        <v>13.37948717948718</v>
       </c>
       <c r="S14" t="n">
-        <v>23.45037841796875</v>
+        <v>12.85225677490234</v>
       </c>
       <c r="T14" t="n">
-        <v>19.19219589233398</v>
+        <v>24.09377288818359</v>
       </c>
       <c r="U14" t="n">
-        <v>19.60490036010742</v>
+        <v>22.90938949584961</v>
       </c>
       <c r="V14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W14" t="n">
-        <v>1.889046381698921</v>
+        <v>2.20745316421638</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -1731,88 +1731,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5_stack2-4</t>
+          <t>4_stack5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>50.17545814871638</v>
+        <v>8.299610212567741</v>
       </c>
       <c r="G15" t="n">
-        <v>7.992832882661181</v>
+        <v>3.250752517268741</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03290750760438533</v>
+        <v>0.03343480064562755</v>
       </c>
       <c r="I15" t="n">
-        <v>1.197972589370386</v>
+        <v>0.5634359326011884</v>
       </c>
       <c r="J15" t="n">
-        <v>52.51589632983411</v>
+        <v>4.036078847364684</v>
       </c>
       <c r="K15" t="n">
-        <v>13.27219718930485</v>
+        <v>4.712532271705335</v>
       </c>
       <c r="L15" t="n">
-        <v>6.108366959878627</v>
+        <v>2.092191005101498</v>
       </c>
       <c r="M15" t="n">
-        <v>1524.741975354885</v>
+        <v>248.2326812872182</v>
       </c>
       <c r="N15" t="n">
-        <v>1997.399392133517</v>
+        <v>176.271124074008</v>
       </c>
       <c r="O15" t="n">
-        <v>1070.651897613995</v>
+        <v>1349.437254317734</v>
       </c>
       <c r="P15" t="n">
-        <v>74.11561584472656</v>
+        <v>76.14286041259766</v>
       </c>
       <c r="Q15" t="n">
-        <v>272.4077453613281</v>
+        <v>220.4149932861328</v>
       </c>
       <c r="R15" t="n">
-        <v>7.188640973630831</v>
+        <v>11.35714285714286</v>
       </c>
       <c r="S15" t="n">
-        <v>23.15008544921875</v>
+        <v>12.1615104675293</v>
       </c>
       <c r="T15" t="n">
-        <v>19.32438659667969</v>
+        <v>21.58454895019531</v>
       </c>
       <c r="U15" t="n">
-        <v>19.60808563232422</v>
+        <v>21.48779296875</v>
       </c>
       <c r="V15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W15" t="n">
-        <v>1.889353301236656</v>
+        <v>2.070474055604447</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -1821,19 +1821,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AB15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack1-4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1845,64 +1845,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>201.6347583456117</v>
+        <v>105.5476036149093</v>
       </c>
       <c r="G16" t="n">
-        <v>16.02277591176857</v>
+        <v>11.59255721463278</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2828051681864789</v>
+        <v>0.102003705707875</v>
       </c>
       <c r="I16" t="n">
-        <v>1.573404666389594</v>
+        <v>1.577234668001973</v>
       </c>
       <c r="J16" t="n">
-        <v>204.8159938407623</v>
+        <v>102.293164350068</v>
       </c>
       <c r="K16" t="n">
-        <v>14.10487492199147</v>
+        <v>13.96675211202239</v>
       </c>
       <c r="L16" t="n">
-        <v>12.23914633253405</v>
+        <v>11.60643684099987</v>
       </c>
       <c r="M16" t="n">
-        <v>712.9811652262866</v>
+        <v>1034.742834904288</v>
       </c>
       <c r="N16" t="n">
-        <v>584.7587590302891</v>
+        <v>1485.495179598985</v>
       </c>
       <c r="O16" t="n">
-        <v>764.4038685639821</v>
+        <v>2598.557289793438</v>
       </c>
       <c r="P16" t="n">
-        <v>68.61502838134766</v>
+        <v>88.97058868408203</v>
       </c>
       <c r="Q16" t="n">
-        <v>331.8374328613281</v>
+        <v>365.7790222167969</v>
       </c>
       <c r="R16" t="n">
-        <v>6.601554404145078</v>
+        <v>5.770152505446623</v>
       </c>
       <c r="S16" t="n">
-        <v>23.01996231079102</v>
+        <v>29.23386383056641</v>
       </c>
       <c r="T16" t="n">
-        <v>14.63066864013672</v>
+        <v>18.53488540649414</v>
       </c>
       <c r="U16" t="n">
-        <v>17.38174057006836</v>
+        <v>19.37087631225586</v>
       </c>
       <c r="V16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.674831982228807</v>
+        <v>1.866496801098956</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -1911,19 +1911,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack1-4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1935,64 +1935,64 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>113.8658217856859</v>
+        <v>45.41324545693446</v>
       </c>
       <c r="G17" t="n">
-        <v>12.0407004402278</v>
+        <v>7.604073906172495</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1126110020715735</v>
+        <v>0.237983525824275</v>
       </c>
       <c r="I17" t="n">
-        <v>1.516112330835521</v>
+        <v>1.910871585948732</v>
       </c>
       <c r="J17" t="n">
-        <v>111.8658672821975</v>
+        <v>47.14400652296509</v>
       </c>
       <c r="K17" t="n">
-        <v>12.30808736079084</v>
+        <v>7.510745707888075</v>
       </c>
       <c r="L17" t="n">
-        <v>12.0629447731757</v>
+        <v>6.113659026114961</v>
       </c>
       <c r="M17" t="n">
-        <v>1011.142958423502</v>
+        <v>190.8251644715409</v>
       </c>
       <c r="N17" t="n">
-        <v>1085.874064571643</v>
+        <v>130.133834532269</v>
       </c>
       <c r="O17" t="n">
-        <v>812.9735662278196</v>
+        <v>2598.557289793438</v>
       </c>
       <c r="P17" t="n">
-        <v>92.78072357177734</v>
+        <v>61.47547912597656</v>
       </c>
       <c r="Q17" t="n">
-        <v>278.6717834472656</v>
+        <v>304.2307739257812</v>
       </c>
       <c r="R17" t="n">
-        <v>6.555020080321285</v>
+        <v>10.0319829424307</v>
       </c>
       <c r="S17" t="n">
-        <v>21.50339508056641</v>
+        <v>35.80643463134766</v>
       </c>
       <c r="T17" t="n">
-        <v>14.18324661254883</v>
+        <v>18.73827362060547</v>
       </c>
       <c r="U17" t="n">
-        <v>15.7027587890625</v>
+        <v>19.37454605102539</v>
       </c>
       <c r="V17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.513052304694647</v>
+        <v>1.866850401811891</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -2001,19 +2001,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack2-4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2022,67 +2022,67 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>107.3398432716536</v>
+        <v>140.6022927638413</v>
       </c>
       <c r="G18" t="n">
-        <v>11.69056599053886</v>
+        <v>13.37985049346043</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1651230425417655</v>
+        <v>0.1646634703696119</v>
       </c>
       <c r="I18" t="n">
-        <v>1.438718350369811</v>
+        <v>1.108304360448542</v>
       </c>
       <c r="J18" t="n">
-        <v>117.2719664550843</v>
+        <v>132.5928990639677</v>
       </c>
       <c r="K18" t="n">
-        <v>13.62256659733793</v>
+        <v>13.85652443028741</v>
       </c>
       <c r="L18" t="n">
-        <v>8.706859674363502</v>
+        <v>10.78744456562013</v>
       </c>
       <c r="M18" t="n">
-        <v>650.0597470792334</v>
+        <v>853.8766518660045</v>
       </c>
       <c r="N18" t="n">
-        <v>809.0503273212091</v>
+        <v>979.0050367555742</v>
       </c>
       <c r="O18" t="n">
-        <v>1161.867202192688</v>
+        <v>1125.106453637748</v>
       </c>
       <c r="P18" t="n">
-        <v>118.3539047241211</v>
+        <v>62.54329299926758</v>
       </c>
       <c r="Q18" t="n">
-        <v>661.4269409179688</v>
+        <v>251.7646179199219</v>
       </c>
       <c r="R18" t="n">
-        <v>6.1099324975892</v>
+        <v>5.990009514747859</v>
       </c>
       <c r="S18" t="n">
-        <v>11.93345260620117</v>
+        <v>20.9851188659668</v>
       </c>
       <c r="T18" t="n">
-        <v>8.294502258300781</v>
+        <v>18.9344367980957</v>
       </c>
       <c r="U18" t="n">
-        <v>8.815467834472656</v>
+        <v>19.37041091918945</v>
       </c>
       <c r="V18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8494216909961662</v>
+        <v>1.866451957765299</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -2091,19 +2091,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack2-4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2112,67 +2112,67 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>2.085875587474972</v>
+        <v>113.7217972777936</v>
       </c>
       <c r="G19" t="n">
-        <v>1.629668458113743</v>
+        <v>12.03308312081498</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002374083628398943</v>
+        <v>0.05107320861566589</v>
       </c>
       <c r="I19" t="n">
-        <v>1.422745106157865</v>
+        <v>1.295822360397382</v>
       </c>
       <c r="J19" t="n">
-        <v>1.504198903309425</v>
+        <v>102.2023692170689</v>
       </c>
       <c r="K19" t="n">
-        <v>2.033988971161878</v>
+        <v>13.23769378265101</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7996796383834807</v>
+        <v>11.80227140798951</v>
       </c>
       <c r="M19" t="n">
-        <v>878.6024057971645</v>
+        <v>2226.642898697992</v>
       </c>
       <c r="N19" t="n">
-        <v>1086.384085629503</v>
+        <v>3154.362545692942</v>
       </c>
       <c r="O19" t="n">
-        <v>764.4038685639821</v>
+        <v>1125.106453637748</v>
       </c>
       <c r="P19" t="n">
-        <v>44.875</v>
+        <v>67.34125518798828</v>
       </c>
       <c r="Q19" t="n">
-        <v>371.2244262695312</v>
+        <v>204.7052154541016</v>
       </c>
       <c r="R19" t="n">
-        <v>3.125</v>
+        <v>6.437262357414449</v>
       </c>
       <c r="S19" t="n">
-        <v>24.64285659790039</v>
+        <v>23.91337585449219</v>
       </c>
       <c r="T19" t="n">
-        <v>17.32064056396484</v>
+        <v>18.45420837402344</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3800163269043</v>
+        <v>19.37316513061523</v>
       </c>
       <c r="V19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W19" t="n">
-        <v>1.674665841353291</v>
+        <v>1.866717342084155</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -2181,19 +2181,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2205,64 +2205,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>35.81258519050321</v>
+        <v>96.95119108165574</v>
       </c>
       <c r="G20" t="n">
-        <v>6.752629092712374</v>
+        <v>11.11044960360917</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05146400258269424</v>
+        <v>0.09953188980586478</v>
       </c>
       <c r="I20" t="n">
-        <v>1.075135425028072</v>
+        <v>1.53743212489533</v>
       </c>
       <c r="J20" t="n">
-        <v>40.29378208305531</v>
+        <v>93.79343563472933</v>
       </c>
       <c r="K20" t="n">
-        <v>6.575475942944529</v>
+        <v>12.02014911482921</v>
       </c>
       <c r="L20" t="n">
-        <v>4.381405843250322</v>
+        <v>12.00364690355332</v>
       </c>
       <c r="M20" t="n">
-        <v>695.876406677818</v>
+        <v>974.0716394590453</v>
       </c>
       <c r="N20" t="n">
-        <v>869.3505093158118</v>
+        <v>1393.259832904573</v>
       </c>
       <c r="O20" t="n">
-        <v>514.3366206566313</v>
+        <v>830.1181202497072</v>
       </c>
       <c r="P20" t="n">
-        <v>89.83380126953125</v>
+        <v>99.77192687988281</v>
       </c>
       <c r="Q20" t="n">
-        <v>312.6773376464844</v>
+        <v>229.0110168457031</v>
       </c>
       <c r="R20" t="n">
-        <v>3.698591549295775</v>
+        <v>6.473684210526316</v>
       </c>
       <c r="S20" t="n">
-        <v>19.8297119140625</v>
+        <v>22.83287048339844</v>
       </c>
       <c r="T20" t="n">
-        <v>18.44392013549805</v>
+        <v>14.85130310058594</v>
       </c>
       <c r="U20" t="n">
-        <v>18.54631805419922</v>
+        <v>16.25333023071289</v>
       </c>
       <c r="V20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W20" t="n">
-        <v>1.787045808476144</v>
+        <v>1.566103071115922</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -2271,19 +2271,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2298,61 +2298,61 @@
         <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>7.801744604228981</v>
+        <v>10.5198191289849</v>
       </c>
       <c r="G21" t="n">
-        <v>3.151743921708825</v>
+        <v>3.659815530663395</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01054574820626301</v>
+        <v>0.01079984130820924</v>
       </c>
       <c r="I21" t="n">
-        <v>1.269031953236061</v>
+        <v>0.7160482235605999</v>
       </c>
       <c r="J21" t="n">
-        <v>5.383348194409691</v>
+        <v>6.401480578871632</v>
       </c>
       <c r="K21" t="n">
-        <v>8.452171571467112</v>
+        <v>3.258324042490942</v>
       </c>
       <c r="L21" t="n">
-        <v>1.791152272582819</v>
+        <v>2.626138457690976</v>
       </c>
       <c r="M21" t="n">
-        <v>739.8000077031622</v>
+        <v>974.0716394590453</v>
       </c>
       <c r="N21" t="n">
-        <v>821.9577833239575</v>
+        <v>1393.259832904573</v>
       </c>
       <c r="O21" t="n">
-        <v>378.08253343005</v>
+        <v>64.85113912627091</v>
       </c>
       <c r="P21" t="n">
-        <v>59.1929817199707</v>
+        <v>57.55339813232422</v>
       </c>
       <c r="Q21" t="n">
-        <v>308.6145629882812</v>
+        <v>229.0110168457031</v>
       </c>
       <c r="R21" t="n">
-        <v>9.105263157894736</v>
+        <v>10.57281553398058</v>
       </c>
       <c r="S21" t="n">
-        <v>23.421875</v>
+        <v>10.41498565673828</v>
       </c>
       <c r="T21" t="n">
-        <v>18.45648956298828</v>
+        <v>14.54508972167969</v>
       </c>
       <c r="U21" t="n">
-        <v>18.57220840454102</v>
+        <v>14.19417190551758</v>
       </c>
       <c r="V21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W21" t="n">
-        <v>1.789540494587051</v>
+        <v>1.367691168371923</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2361,10 +2361,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
@@ -2373,7 +2373,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2385,64 +2385,64 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>3.428392670130564</v>
+        <v>8.731901203885307</v>
       </c>
       <c r="G22" t="n">
-        <v>2.089297758216958</v>
+        <v>3.334336802650169</v>
       </c>
       <c r="H22" t="n">
-        <v>0.004634215510181739</v>
+        <v>0.009947419084446952</v>
       </c>
       <c r="I22" t="n">
-        <v>1.429923369235175</v>
+        <v>1.276233094488507</v>
       </c>
       <c r="J22" t="n">
-        <v>1.741502968962831</v>
+        <v>7.999422110367494</v>
       </c>
       <c r="K22" t="n">
-        <v>6.071494920142931</v>
+        <v>4.896207690951348</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5197760763066344</v>
+        <v>3.237261894490558</v>
       </c>
       <c r="M22" t="n">
-        <v>739.8000077031622</v>
+        <v>877.8057031434276</v>
       </c>
       <c r="N22" t="n">
-        <v>821.9577833239575</v>
+        <v>1086.541015185767</v>
       </c>
       <c r="O22" t="n">
-        <v>427.0445549845486</v>
+        <v>1031.576438104154</v>
       </c>
       <c r="P22" t="n">
-        <v>41.33333206176758</v>
+        <v>62.71186447143555</v>
       </c>
       <c r="Q22" t="n">
-        <v>308.6145629882812</v>
+        <v>344.8912658691406</v>
       </c>
       <c r="R22" t="n">
-        <v>12.22222222222222</v>
+        <v>4.47457627118644</v>
       </c>
       <c r="S22" t="n">
-        <v>21.48554992675781</v>
+        <v>22.42569351196289</v>
       </c>
       <c r="T22" t="n">
-        <v>15.02566528320312</v>
+        <v>17.57178497314453</v>
       </c>
       <c r="U22" t="n">
-        <v>15.10046768188477</v>
+        <v>17.64904022216797</v>
       </c>
       <c r="V22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W22" t="n">
-        <v>1.455018047144495</v>
+        <v>1.700587861185255</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2451,19 +2451,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5_stack4-3</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2472,67 +2472,67 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>46.52839694260095</v>
+        <v>2.085875587474972</v>
       </c>
       <c r="G23" t="n">
-        <v>7.696869164826317</v>
+        <v>1.629668458113743</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09870840006395322</v>
+        <v>0.002376238363461799</v>
       </c>
       <c r="I23" t="n">
-        <v>2.942761258362216</v>
+        <v>1.665803333939317</v>
       </c>
       <c r="J23" t="n">
-        <v>52.73688478150276</v>
+        <v>1.504198903309425</v>
       </c>
       <c r="K23" t="n">
-        <v>7.28966856338082</v>
+        <v>2.033988971161878</v>
       </c>
       <c r="L23" t="n">
-        <v>6.737000791485979</v>
+        <v>0.7996796383834807</v>
       </c>
       <c r="M23" t="n">
-        <v>471.3722126227877</v>
+        <v>877.8057031434276</v>
       </c>
       <c r="N23" t="n">
-        <v>498.2121087504623</v>
+        <v>1086.541015185767</v>
       </c>
       <c r="O23" t="n">
-        <v>279.6484692631936</v>
+        <v>329.5520681552786</v>
       </c>
       <c r="P23" t="n">
-        <v>66.21759033203125</v>
+        <v>44.875</v>
       </c>
       <c r="Q23" t="n">
-        <v>386.1875</v>
+        <v>344.8912658691406</v>
       </c>
       <c r="R23" t="n">
-        <v>4.421296296296297</v>
+        <v>3.125</v>
       </c>
       <c r="S23" t="n">
-        <v>15.20980453491211</v>
+        <v>24.64285659790039</v>
       </c>
       <c r="T23" t="n">
-        <v>5.168548583984375</v>
+        <v>14.79337692260742</v>
       </c>
       <c r="U23" t="n">
-        <v>6.801361083984375</v>
+        <v>14.93109130859375</v>
       </c>
       <c r="V23" t="n">
         <v>30</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6553507699774984</v>
+        <v>1.438697646671471</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2541,10 +2541,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="b">
         <v>0</v>
@@ -2553,7 +2553,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack3-6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2565,64 +2565,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>304.9659770160591</v>
+        <v>36.60088930737363</v>
       </c>
       <c r="G24" t="n">
-        <v>19.70519580556461</v>
+        <v>6.826543754977513</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4779038302053868</v>
+        <v>0.05304819248859279</v>
       </c>
       <c r="I24" t="n">
-        <v>2.112143853643803</v>
+        <v>1.014369849598692</v>
       </c>
       <c r="J24" t="n">
-        <v>319.3125067182499</v>
+        <v>39.55791534708321</v>
       </c>
       <c r="K24" t="n">
-        <v>15.16831949002917</v>
+        <v>7.124096481281727</v>
       </c>
       <c r="L24" t="n">
-        <v>10.51623635178903</v>
+        <v>4.603168408349381</v>
       </c>
       <c r="M24" t="n">
-        <v>638.1325232003165</v>
+        <v>689.9554459889299</v>
       </c>
       <c r="N24" t="n">
-        <v>417.2364577180225</v>
+        <v>860.1701302743434</v>
       </c>
       <c r="O24" t="n">
-        <v>994.65875999295</v>
+        <v>735.9603864910562</v>
       </c>
       <c r="P24" t="n">
-        <v>127.6974716186523</v>
+        <v>109.1253814697266</v>
       </c>
       <c r="Q24" t="n">
-        <v>258.9946899414062</v>
+        <v>190.6574249267578</v>
       </c>
       <c r="R24" t="n">
-        <v>9.686949104350299</v>
+        <v>4.051987767584098</v>
       </c>
       <c r="S24" t="n">
-        <v>17.92666625976562</v>
+        <v>19.77242660522461</v>
       </c>
       <c r="T24" t="n">
-        <v>8.4874267578125</v>
+        <v>19.49232482910156</v>
       </c>
       <c r="U24" t="n">
-        <v>11.24206924438477</v>
+        <v>19.50852584838867</v>
       </c>
       <c r="V24" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.263778727302044</v>
+        <v>1.879760135948815</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -2631,19 +2631,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AB24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack3-6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2655,64 +2655,64 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>184.1591179906977</v>
+        <v>7.801744604228981</v>
       </c>
       <c r="G25" t="n">
-        <v>15.31269641667675</v>
+        <v>3.151743921708825</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2485107871661424</v>
+        <v>0.01096385430290432</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8263610748041064</v>
+        <v>1.236748356448535</v>
       </c>
       <c r="J25" t="n">
-        <v>190.4192422072453</v>
+        <v>5.383348194409691</v>
       </c>
       <c r="K25" t="n">
-        <v>14.07066198930459</v>
+        <v>8.452171571467112</v>
       </c>
       <c r="L25" t="n">
-        <v>8.451673588476918</v>
+        <v>1.791152272582819</v>
       </c>
       <c r="M25" t="n">
-        <v>741.0508014188446</v>
+        <v>711.5877672838375</v>
       </c>
       <c r="N25" t="n">
-        <v>484.5200049663918</v>
+        <v>736.4311751598494</v>
       </c>
       <c r="O25" t="n">
-        <v>994.65875999295</v>
+        <v>326.2173150846597</v>
       </c>
       <c r="P25" t="n">
-        <v>140.5452423095703</v>
+        <v>59.1929817199707</v>
       </c>
       <c r="Q25" t="n">
-        <v>269.7634582519531</v>
+        <v>263.4835510253906</v>
       </c>
       <c r="R25" t="n">
-        <v>9.587965089572807</v>
+        <v>9.105263157894736</v>
       </c>
       <c r="S25" t="n">
-        <v>9.598869323730469</v>
+        <v>23.421875</v>
       </c>
       <c r="T25" t="n">
-        <v>11.61582946777344</v>
+        <v>18.93827056884766</v>
       </c>
       <c r="U25" t="n">
-        <v>11.24148941040039</v>
+        <v>19.05930328369141</v>
       </c>
       <c r="V25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="W25" t="n">
-        <v>1.263713545186644</v>
+        <v>1.836474924352145</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -2721,10 +2721,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AB25" t="b">
         <v>0</v>
@@ -2733,7 +2733,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack3-6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2745,64 +2745,64 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>138.9471527717982</v>
+        <v>3.428392670130564</v>
       </c>
       <c r="G26" t="n">
-        <v>13.30086499207519</v>
+        <v>2.089297758216958</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1598201037208242</v>
+        <v>0.004817947732880363</v>
       </c>
       <c r="I26" t="n">
-        <v>1.608749450645684</v>
+        <v>1.068101191743832</v>
       </c>
       <c r="J26" t="n">
-        <v>139.4372285135029</v>
+        <v>1.741502968962831</v>
       </c>
       <c r="K26" t="n">
-        <v>14.35276779380534</v>
+        <v>6.071494920142931</v>
       </c>
       <c r="L26" t="n">
-        <v>10.47157228897981</v>
+        <v>0.5197760763066344</v>
       </c>
       <c r="M26" t="n">
-        <v>869.3972130972516</v>
+        <v>711.5877672838375</v>
       </c>
       <c r="N26" t="n">
-        <v>548.5864963113406</v>
+        <v>736.4311751598494</v>
       </c>
       <c r="O26" t="n">
-        <v>2102.777589165074</v>
+        <v>1093.05359177074</v>
       </c>
       <c r="P26" t="n">
-        <v>94.63245391845703</v>
+        <v>41.33333206176758</v>
       </c>
       <c r="Q26" t="n">
-        <v>292.4730529785156</v>
+        <v>263.4835510253906</v>
       </c>
       <c r="R26" t="n">
-        <v>5.672737306843267</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="S26" t="n">
-        <v>22.70526123046875</v>
+        <v>21.48554992675781</v>
       </c>
       <c r="T26" t="n">
-        <v>14.11360931396484</v>
+        <v>20.11565017700195</v>
       </c>
       <c r="U26" t="n">
-        <v>15.1231803894043</v>
+        <v>20.12346267700195</v>
       </c>
       <c r="V26" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="W26" t="n">
-        <v>1.70007435907112</v>
+        <v>1.93901288244219</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
@@ -2811,19 +2811,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AB26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2832,67 +2832,67 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>92.06358371292499</v>
+        <v>112.0490761363225</v>
       </c>
       <c r="G27" t="n">
-        <v>10.82677216040553</v>
+        <v>11.94425864956912</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05752003284343651</v>
+        <v>0.1107586237662319</v>
       </c>
       <c r="I27" t="n">
-        <v>1.854136824217719</v>
+        <v>2.033693665917514</v>
       </c>
       <c r="J27" t="n">
-        <v>86.25508774026692</v>
+        <v>117.0146931095369</v>
       </c>
       <c r="K27" t="n">
-        <v>12.00575529533505</v>
+        <v>11.58079108856258</v>
       </c>
       <c r="L27" t="n">
-        <v>10.76540139460322</v>
+        <v>10.12496176282187</v>
       </c>
       <c r="M27" t="n">
-        <v>1600.548177076192</v>
+        <v>1011.651032905702</v>
       </c>
       <c r="N27" t="n">
-        <v>1328.212531832971</v>
+        <v>1403.813345563355</v>
       </c>
       <c r="O27" t="n">
-        <v>1403.852577952421</v>
+        <v>946.0105975509803</v>
       </c>
       <c r="P27" t="n">
-        <v>54.32064056396484</v>
+        <v>64.20115661621094</v>
       </c>
       <c r="Q27" t="n">
-        <v>280.1983032226562</v>
+        <v>181.9292144775391</v>
       </c>
       <c r="R27" t="n">
-        <v>8.939803439803439</v>
+        <v>6.032976092333058</v>
       </c>
       <c r="S27" t="n">
-        <v>30.37189483642578</v>
+        <v>43.02751159667969</v>
       </c>
       <c r="T27" t="n">
-        <v>16.38061141967773</v>
+        <v>21.15732192993164</v>
       </c>
       <c r="U27" t="n">
-        <v>18.03057479858398</v>
+        <v>24.35424423217773</v>
       </c>
       <c r="V27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W27" t="n">
-        <v>2.026909492917448</v>
+        <v>2.346673336806241</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -2901,19 +2901,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2922,67 +2922,67 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>62.01063081907365</v>
+        <v>45.53309471069962</v>
       </c>
       <c r="G28" t="n">
-        <v>8.885628134961399</v>
+        <v>7.614101180036566</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1025620506503091</v>
+        <v>0.09132810893583294</v>
       </c>
       <c r="I28" t="n">
-        <v>1.847856432082134</v>
+        <v>2.492789860365837</v>
       </c>
       <c r="J28" t="n">
-        <v>56.33289645678693</v>
+        <v>51.9657709155824</v>
       </c>
       <c r="K28" t="n">
-        <v>11.77676807506688</v>
+        <v>6.465727412221991</v>
       </c>
       <c r="L28" t="n">
-        <v>8.502235368679672</v>
+        <v>6.403805078529096</v>
       </c>
       <c r="M28" t="n">
-        <v>604.6157465250209</v>
+        <v>498.5660520211925</v>
       </c>
       <c r="N28" t="n">
-        <v>347.5205023475546</v>
+        <v>522.850049083976</v>
       </c>
       <c r="O28" t="n">
-        <v>2102.777589165074</v>
+        <v>194.2003258772178</v>
       </c>
       <c r="P28" t="n">
-        <v>64.85646820068359</v>
+        <v>76.60713958740234</v>
       </c>
       <c r="Q28" t="n">
-        <v>289.1628112792969</v>
+        <v>296.184814453125</v>
       </c>
       <c r="R28" t="n">
-        <v>7.225552050473186</v>
+        <v>4.163690476190476</v>
       </c>
       <c r="S28" t="n">
-        <v>26.59269714355469</v>
+        <v>15.36088180541992</v>
       </c>
       <c r="T28" t="n">
-        <v>14.39110565185547</v>
+        <v>6.162124633789062</v>
       </c>
       <c r="U28" t="n">
-        <v>15.13563537597656</v>
+        <v>8.062900543212891</v>
       </c>
       <c r="V28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W28" t="n">
-        <v>1.701474488063096</v>
+        <v>0.7769074474944753</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -2991,19 +2991,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3012,67 +3012,67 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>51.58748192829952</v>
+        <v>23.04820429852552</v>
       </c>
       <c r="G29" t="n">
-        <v>8.104518616452276</v>
+        <v>5.41718424534533</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0794460761578349</v>
+        <v>0.0227827615935167</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6084888050014662</v>
+        <v>2.031709996662402</v>
       </c>
       <c r="J29" t="n">
-        <v>48.42808894193212</v>
+        <v>24.3140351748881</v>
       </c>
       <c r="K29" t="n">
-        <v>12.68865415452797</v>
+        <v>5.211333148845979</v>
       </c>
       <c r="L29" t="n">
-        <v>7.941210755473424</v>
+        <v>4.347343405962934</v>
       </c>
       <c r="M29" t="n">
-        <v>649.3395825592579</v>
+        <v>1011.651032905702</v>
       </c>
       <c r="N29" t="n">
-        <v>500.4483549272303</v>
+        <v>1403.813345563355</v>
       </c>
       <c r="O29" t="n">
-        <v>2102.777589165074</v>
+        <v>91.80379041468477</v>
       </c>
       <c r="P29" t="n">
-        <v>83.31683349609375</v>
+        <v>44.7634391784668</v>
       </c>
       <c r="Q29" t="n">
-        <v>293.0243835449219</v>
+        <v>181.9292144775391</v>
       </c>
       <c r="R29" t="n">
-        <v>8.096534653465346</v>
+        <v>2.510752688172043</v>
       </c>
       <c r="S29" t="n">
-        <v>9.388267517089844</v>
+        <v>57.79798126220703</v>
       </c>
       <c r="T29" t="n">
-        <v>15.42882537841797</v>
+        <v>28.44794845581055</v>
       </c>
       <c r="U29" t="n">
-        <v>15.12361145019531</v>
+        <v>33.1793212890625</v>
       </c>
       <c r="V29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W29" t="n">
-        <v>1.700122816827964</v>
+        <v>3.197020932371934</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
@@ -3081,19 +3081,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3102,67 +3102,67 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>27.85728706618427</v>
+        <v>21.58992608551589</v>
       </c>
       <c r="G30" t="n">
-        <v>5.955585571688581</v>
+        <v>5.243009408725876</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1045549087575192</v>
+        <v>0.02134127815152276</v>
       </c>
       <c r="I30" t="n">
-        <v>1.71912936344611</v>
+        <v>2.587593449478455</v>
       </c>
       <c r="J30" t="n">
-        <v>25.27574758897293</v>
+        <v>20.53348573841836</v>
       </c>
       <c r="K30" t="n">
-        <v>7.456074474718609</v>
+        <v>4.897820056941097</v>
       </c>
       <c r="L30" t="n">
-        <v>6.422344231177331</v>
+        <v>2.819530846696294</v>
       </c>
       <c r="M30" t="n">
-        <v>266.4369124054243</v>
+        <v>1011.651032905702</v>
       </c>
       <c r="N30" t="n">
-        <v>149.9461910106518</v>
+        <v>1403.813345563355</v>
       </c>
       <c r="O30" t="n">
-        <v>1403.852577952421</v>
+        <v>168.5031110389193</v>
       </c>
       <c r="P30" t="n">
-        <v>84.49826812744141</v>
+        <v>45.51694869995117</v>
       </c>
       <c r="Q30" t="n">
-        <v>291.124267578125</v>
+        <v>181.9292144775391</v>
       </c>
       <c r="R30" t="n">
-        <v>3.688581314878893</v>
+        <v>3.957627118644068</v>
       </c>
       <c r="S30" t="n">
-        <v>30.07947158813477</v>
+        <v>51.13585662841797</v>
       </c>
       <c r="T30" t="n">
-        <v>17.49692153930664</v>
+        <v>19.76193618774414</v>
       </c>
       <c r="U30" t="n">
-        <v>18.03057479858398</v>
+        <v>22.55403137207031</v>
       </c>
       <c r="V30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W30" t="n">
-        <v>2.026909492917448</v>
+        <v>2.173212338422715</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
@@ -3171,19 +3171,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3192,67 +3192,67 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>15.73448376177875</v>
+        <v>9.921895122498064</v>
       </c>
       <c r="G31" t="n">
-        <v>4.475909621684734</v>
+        <v>3.554286036418491</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00983068425376722</v>
+        <v>0.0199008638519903</v>
       </c>
       <c r="I31" t="n">
-        <v>2.365117974405798</v>
+        <v>1.362596109405644</v>
       </c>
       <c r="J31" t="n">
-        <v>13.22202128599921</v>
+        <v>6.915321099244549</v>
       </c>
       <c r="K31" t="n">
-        <v>4.703589713145639</v>
+        <v>5.365853976173806</v>
       </c>
       <c r="L31" t="n">
-        <v>4.073009369404259</v>
+        <v>1.69332527090525</v>
       </c>
       <c r="M31" t="n">
-        <v>1600.548177076192</v>
+        <v>498.5660520211925</v>
       </c>
       <c r="N31" t="n">
-        <v>1328.212531832971</v>
+        <v>522.850049083976</v>
       </c>
       <c r="O31" t="n">
-        <v>2102.777589165074</v>
+        <v>235.158940062231</v>
       </c>
       <c r="P31" t="n">
-        <v>76.63934326171875</v>
+        <v>66.80999755859375</v>
       </c>
       <c r="Q31" t="n">
-        <v>280.1983032226562</v>
+        <v>296.184814453125</v>
       </c>
       <c r="R31" t="n">
-        <v>9.262295081967213</v>
+        <v>5.15</v>
       </c>
       <c r="S31" t="n">
-        <v>35</v>
+        <v>7.163978576660156</v>
       </c>
       <c r="T31" t="n">
-        <v>14.79841613769531</v>
+        <v>5.257595062255859</v>
       </c>
       <c r="U31" t="n">
-        <v>15.13520431518555</v>
+        <v>5.348758697509766</v>
       </c>
       <c r="V31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W31" t="n">
-        <v>1.701426030306253</v>
+        <v>0.5153840661527388</v>
       </c>
       <c r="X31" t="n">
         <v>1</v>
@@ -3261,88 +3261,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6_stack1-4</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" t="n">
-        <v>40.94697337053171</v>
+        <v>193.9078911847606</v>
       </c>
       <c r="G32" t="n">
-        <v>7.220478220490567</v>
+        <v>15.71277171897562</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04157750374221694</v>
+        <v>0.2385338574566688</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9424035186904762</v>
+        <v>1.17553765042985</v>
       </c>
       <c r="J32" t="n">
-        <v>35.05017586359902</v>
+        <v>183.345910803501</v>
       </c>
       <c r="K32" t="n">
-        <v>9.350297077835789</v>
+        <v>13.13459811537022</v>
       </c>
       <c r="L32" t="n">
-        <v>4.418845894935973</v>
+        <v>12.49634604136964</v>
       </c>
       <c r="M32" t="n">
-        <v>984.8348189541498</v>
+        <v>812.9155888068642</v>
       </c>
       <c r="N32" t="n">
-        <v>1343.003142510893</v>
+        <v>900.1479347327039</v>
       </c>
       <c r="O32" t="n">
-        <v>948.2468437277482</v>
+        <v>1224.639024698455</v>
       </c>
       <c r="P32" t="n">
-        <v>70.25707244873047</v>
+        <v>56.59135055541992</v>
       </c>
       <c r="Q32" t="n">
-        <v>431.3583374023438</v>
+        <v>283.7093505859375</v>
       </c>
       <c r="R32" t="n">
-        <v>6.129716981132075</v>
+        <v>7.914594594594595</v>
       </c>
       <c r="S32" t="n">
-        <v>11.20417785644531</v>
+        <v>20.39044189453125</v>
       </c>
       <c r="T32" t="n">
-        <v>11.88893890380859</v>
+        <v>17.34563064575195</v>
       </c>
       <c r="U32" t="n">
-        <v>11.84683609008789</v>
+        <v>18.13009262084961</v>
       </c>
       <c r="V32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W32" t="n">
-        <v>1.141511685318155</v>
+        <v>1.746940062749424</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
@@ -3351,88 +3351,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6_stack1-4</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>26.80086460241832</v>
+        <v>107.3026456307283</v>
       </c>
       <c r="G33" t="n">
-        <v>5.841568337774698</v>
+        <v>11.68854018565822</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03511805785476238</v>
+        <v>0.07737590094050864</v>
       </c>
       <c r="I33" t="n">
-        <v>1.620149353313662</v>
+        <v>1.263225173950195</v>
       </c>
       <c r="J33" t="n">
-        <v>18.19012881466651</v>
+        <v>103.711050769309</v>
       </c>
       <c r="K33" t="n">
-        <v>8.7432852449531</v>
+        <v>11.43323869096514</v>
       </c>
       <c r="L33" t="n">
-        <v>4.866158139926085</v>
+        <v>6.782566986912284</v>
       </c>
       <c r="M33" t="n">
-        <v>763.1647716185944</v>
+        <v>1386.770872150868</v>
       </c>
       <c r="N33" t="n">
-        <v>826.9795291244188</v>
+        <v>1779.306541315042</v>
       </c>
       <c r="O33" t="n">
-        <v>948.2468437277482</v>
+        <v>213.1103374070802</v>
       </c>
       <c r="P33" t="n">
-        <v>56.62136077880859</v>
+        <v>49.57143020629883</v>
       </c>
       <c r="Q33" t="n">
-        <v>296.619873046875</v>
+        <v>232.7940521240234</v>
       </c>
       <c r="R33" t="n">
-        <v>5.135922330097087</v>
+        <v>16.55573905862923</v>
       </c>
       <c r="S33" t="n">
-        <v>18.57258987426758</v>
+        <v>12.63225173950195</v>
       </c>
       <c r="T33" t="n">
-        <v>11.46350479125977</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>11.7965087890625</v>
+        <v>11.36629867553711</v>
       </c>
       <c r="V33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W33" t="n">
-        <v>1.136662356621941</v>
+        <v>1.095209105475656</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
@@ -3441,88 +3441,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6_stack2-5</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
-        <v>49.21794601924945</v>
+        <v>84.60826087105715</v>
       </c>
       <c r="G34" t="n">
-        <v>7.916200804827338</v>
+        <v>10.37914175412874</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05109127715984912</v>
+        <v>0.1015448931183933</v>
       </c>
       <c r="I34" t="n">
-        <v>1.489605310018025</v>
+        <v>1.822310435489361</v>
       </c>
       <c r="J34" t="n">
-        <v>45.5700195304811</v>
+        <v>80.12823388485802</v>
       </c>
       <c r="K34" t="n">
-        <v>12.26386482593169</v>
+        <v>9.905138147108945</v>
       </c>
       <c r="L34" t="n">
-        <v>4.499183327394515</v>
+        <v>9.260609566329695</v>
       </c>
       <c r="M34" t="n">
-        <v>963.3336404032613</v>
+        <v>833.2103986008497</v>
       </c>
       <c r="N34" t="n">
-        <v>1239.508100154509</v>
+        <v>819.0545865330657</v>
       </c>
       <c r="O34" t="n">
-        <v>937.8894930142966</v>
+        <v>1411.189034707782</v>
       </c>
       <c r="P34" t="n">
-        <v>60.41164779663086</v>
+        <v>55.38333511352539</v>
       </c>
       <c r="Q34" t="n">
-        <v>427.18896484375</v>
+        <v>158.4251403808594</v>
       </c>
       <c r="R34" t="n">
-        <v>7.198795180722891</v>
+        <v>9.623611111111112</v>
       </c>
       <c r="S34" t="n">
-        <v>18.26920700073242</v>
+        <v>28.54983139038086</v>
       </c>
       <c r="T34" t="n">
-        <v>12.26446151733398</v>
+        <v>15.66683197021484</v>
       </c>
       <c r="U34" t="n">
-        <v>12.71612930297852</v>
+        <v>17.05040740966797</v>
       </c>
       <c r="V34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W34" t="n">
-        <v>1.225273151496678</v>
+        <v>1.642906101643113</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
@@ -3531,10 +3531,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="b">
         <v>0</v>
@@ -3543,76 +3543,76 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6_stack2-5</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>48.83850341545088</v>
+        <v>70.98607444186055</v>
       </c>
       <c r="G35" t="n">
-        <v>7.885627042552505</v>
+        <v>9.506959403767899</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07459399324902768</v>
+        <v>0.08148601149572611</v>
       </c>
       <c r="I35" t="n">
-        <v>2.088198299400609</v>
+        <v>1.293207989826299</v>
       </c>
       <c r="J35" t="n">
-        <v>33.04376062406164</v>
+        <v>50.12392415733655</v>
       </c>
       <c r="K35" t="n">
-        <v>12.11619766562892</v>
+        <v>13.03922259406887</v>
       </c>
       <c r="L35" t="n">
-        <v>7.547398518988195</v>
+        <v>7.40082135952594</v>
       </c>
       <c r="M35" t="n">
-        <v>654.7243455971903</v>
+        <v>871.1442999708451</v>
       </c>
       <c r="N35" t="n">
-        <v>392.0884963266494</v>
+        <v>1083.206262115148</v>
       </c>
       <c r="O35" t="n">
-        <v>937.8894930142966</v>
+        <v>1224.639024698455</v>
       </c>
       <c r="P35" t="n">
-        <v>46.65967559814453</v>
+        <v>62.05330276489258</v>
       </c>
       <c r="Q35" t="n">
-        <v>343.0689392089844</v>
+        <v>202.5839385986328</v>
       </c>
       <c r="R35" t="n">
-        <v>5.317741935483871</v>
+        <v>9.192352259559675</v>
       </c>
       <c r="S35" t="n">
-        <v>24.28726196289062</v>
+        <v>22.79791641235352</v>
       </c>
       <c r="T35" t="n">
-        <v>11.6307258605957</v>
+        <v>17.62896347045898</v>
       </c>
       <c r="U35" t="n">
-        <v>12.74577331542969</v>
+        <v>18.13053894042969</v>
       </c>
       <c r="V35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W35" t="n">
-        <v>1.228129524823312</v>
+        <v>1.746983068241537</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -3621,88 +3621,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6_stack2-5</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
         <v>18</v>
       </c>
       <c r="F36" t="n">
-        <v>43.18087684814019</v>
+        <v>54.88478787165095</v>
       </c>
       <c r="G36" t="n">
-        <v>7.414822990428776</v>
+        <v>8.359514478878951</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07137383807442686</v>
+        <v>0.05253207905084546</v>
       </c>
       <c r="I36" t="n">
-        <v>1.839330137955688</v>
+        <v>1.686667825597837</v>
       </c>
       <c r="J36" t="n">
-        <v>45.97276404475229</v>
+        <v>45.71358096794808</v>
       </c>
       <c r="K36" t="n">
-        <v>8.516579935045026</v>
+        <v>10.79781865809209</v>
       </c>
       <c r="L36" t="n">
-        <v>5.586075648896104</v>
+        <v>8.617657225677537</v>
       </c>
       <c r="M36" t="n">
-        <v>604.9958642144513</v>
+        <v>1044.786135696787</v>
       </c>
       <c r="N36" t="n">
-        <v>658.2802561401691</v>
+        <v>1248.649246806911</v>
       </c>
       <c r="O36" t="n">
-        <v>1125.577242306541</v>
+        <v>1224.639024698455</v>
       </c>
       <c r="P36" t="n">
-        <v>48.17142868041992</v>
+        <v>61.12609481811523</v>
       </c>
       <c r="Q36" t="n">
-        <v>459.5846557617188</v>
+        <v>167.5503540039062</v>
       </c>
       <c r="R36" t="n">
-        <v>8.485714285714286</v>
+        <v>8.455341506129598</v>
       </c>
       <c r="S36" t="n">
-        <v>25.00604629516602</v>
+        <v>29.05429840087891</v>
       </c>
       <c r="T36" t="n">
-        <v>13.59519195556641</v>
+        <v>17.22585678100586</v>
       </c>
       <c r="U36" t="n">
-        <v>14.25668334960938</v>
+        <v>18.14437103271484</v>
       </c>
       <c r="V36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W36" t="n">
-        <v>1.373714510246013</v>
+        <v>1.748315870928756</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -3711,88 +3711,88 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6_stack3-3</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
-        <v>17.12836227578553</v>
+        <v>34.79319733138874</v>
       </c>
       <c r="G37" t="n">
-        <v>4.669958049713092</v>
+        <v>6.655830130802474</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01293346893234969</v>
+        <v>0.03330174103830782</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7118634338135706</v>
+        <v>1.79652994313133</v>
       </c>
       <c r="J37" t="n">
-        <v>17.74034718969782</v>
+        <v>33.46178298838706</v>
       </c>
       <c r="K37" t="n">
-        <v>4.849106830933332</v>
+        <v>7.402556784500822</v>
       </c>
       <c r="L37" t="n">
-        <v>3.984360151188718</v>
+        <v>6.31064822406022</v>
       </c>
       <c r="M37" t="n">
-        <v>1324.344022889591</v>
+        <v>1044.786135696787</v>
       </c>
       <c r="N37" t="n">
-        <v>1982.883408179059</v>
+        <v>1248.649246806911</v>
       </c>
       <c r="O37" t="n">
-        <v>37.27076961279937</v>
+        <v>1411.189034707782</v>
       </c>
       <c r="P37" t="n">
-        <v>72.54666900634766</v>
+        <v>72.50373840332031</v>
       </c>
       <c r="Q37" t="n">
-        <v>300.7000427246094</v>
+        <v>167.5503540039062</v>
       </c>
       <c r="R37" t="n">
-        <v>3.106666666666666</v>
+        <v>4.062344139650873</v>
       </c>
       <c r="S37" t="n">
-        <v>8.846035003662109</v>
+        <v>29.45373916625977</v>
       </c>
       <c r="T37" t="n">
-        <v>12.42658996582031</v>
+        <v>16.39479446411133</v>
       </c>
       <c r="U37" t="n">
-        <v>11.17853164672852</v>
+        <v>17.05040740966797</v>
       </c>
       <c r="V37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W37" t="n">
-        <v>1.256636139709288</v>
+        <v>1.642906101643113</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -3801,10 +3801,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB37" t="b">
         <v>0</v>
@@ -3813,76 +3813,76 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>106.6764928830685</v>
+        <v>5.849635337710113</v>
       </c>
       <c r="G38" t="n">
-        <v>11.65438669481934</v>
+        <v>2.729100041085476</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1089685984630563</v>
+        <v>0.004725459810385082</v>
       </c>
       <c r="I38" t="n">
-        <v>1.110695748214871</v>
+        <v>3.880876674377442</v>
       </c>
       <c r="J38" t="n">
-        <v>100.0792945742637</v>
+        <v>2.012310229912006</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23502944443883</v>
+        <v>6.852833546452089</v>
       </c>
       <c r="L38" t="n">
-        <v>9.525021819027323</v>
+        <v>2.303504015138129</v>
       </c>
       <c r="M38" t="n">
-        <v>978.9654486492742</v>
+        <v>1237.897595669832</v>
       </c>
       <c r="N38" t="n">
-        <v>1271.404032465252</v>
+        <v>1507.19069075254</v>
       </c>
       <c r="O38" t="n">
-        <v>676.1702255543128</v>
+        <v>217.54359737155</v>
       </c>
       <c r="P38" t="n">
-        <v>89.72348022460938</v>
+        <v>63.86956405639648</v>
       </c>
       <c r="Q38" t="n">
-        <v>465.2996215820312</v>
+        <v>115.2356643676758</v>
       </c>
       <c r="R38" t="n">
-        <v>4.231348391512663</v>
+        <v>3.717391304347826</v>
       </c>
       <c r="S38" t="n">
-        <v>17.3127555847168</v>
+        <v>32.70329666137695</v>
       </c>
       <c r="T38" t="n">
-        <v>15.58730697631836</v>
+        <v>8.426780700683594</v>
       </c>
       <c r="U38" t="n">
-        <v>15.88838958740234</v>
+        <v>9.153240203857422</v>
       </c>
       <c r="V38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="W38" t="n">
-        <v>1.786095454062047</v>
+        <v>0.8819680268868867</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -3891,19 +3891,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack1-4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3912,67 +3912,67 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F39" t="n">
-        <v>58.39491977731079</v>
+        <v>39.61973660261321</v>
       </c>
       <c r="G39" t="n">
-        <v>8.622686418518857</v>
+        <v>7.10249360397025</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05964962283181809</v>
+        <v>0.03982109116081892</v>
       </c>
       <c r="I39" t="n">
-        <v>2.019770592608529</v>
+        <v>0.8187250606368829</v>
       </c>
       <c r="J39" t="n">
-        <v>60.87899636201097</v>
+        <v>35.91901761682366</v>
       </c>
       <c r="K39" t="n">
-        <v>9.613368914088458</v>
+        <v>9.303492970272256</v>
       </c>
       <c r="L39" t="n">
-        <v>5.690342708262291</v>
+        <v>4.373488034459501</v>
       </c>
       <c r="M39" t="n">
-        <v>978.9654486492742</v>
+        <v>994.943519819873</v>
       </c>
       <c r="N39" t="n">
-        <v>1271.404032465252</v>
+        <v>1366.071787281762</v>
       </c>
       <c r="O39" t="n">
-        <v>99.8071977841701</v>
+        <v>1028.084755477271</v>
       </c>
       <c r="P39" t="n">
-        <v>68.33928680419922</v>
+        <v>75.52462768554688</v>
       </c>
       <c r="Q39" t="n">
-        <v>465.2996215820312</v>
+        <v>371.948974609375</v>
       </c>
       <c r="R39" t="n">
-        <v>8.382440476190476</v>
+        <v>5.884236453201971</v>
       </c>
       <c r="S39" t="n">
-        <v>28.2926139831543</v>
+        <v>9.899532318115234</v>
       </c>
       <c r="T39" t="n">
-        <v>14.00783538818359</v>
+        <v>12.09140014648438</v>
       </c>
       <c r="U39" t="n">
-        <v>19.43888473510742</v>
+        <v>11.94642639160156</v>
       </c>
       <c r="V39" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="W39" t="n">
-        <v>2.185224843991753</v>
+        <v>1.151107791152465</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -3981,19 +3981,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack1-4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4002,67 +4002,67 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F40" t="n">
-        <v>53.80884738434862</v>
+        <v>26.94105684664718</v>
       </c>
       <c r="G40" t="n">
-        <v>8.277170551968341</v>
+        <v>5.856826696608771</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05496501174642198</v>
+        <v>0.03443994429079371</v>
       </c>
       <c r="I40" t="n">
-        <v>1.523941273928223</v>
+        <v>1.614162974860437</v>
       </c>
       <c r="J40" t="n">
-        <v>52.07861085633662</v>
+        <v>18.19012881466651</v>
       </c>
       <c r="K40" t="n">
-        <v>10.22947152558077</v>
+        <v>8.7432852449531</v>
       </c>
       <c r="L40" t="n">
-        <v>4.656422689057171</v>
+        <v>4.866158139926085</v>
       </c>
       <c r="M40" t="n">
-        <v>978.9654486492742</v>
+        <v>782.2619171265301</v>
       </c>
       <c r="N40" t="n">
-        <v>1271.404032465252</v>
+        <v>860.1701302743434</v>
       </c>
       <c r="O40" t="n">
-        <v>697.9442014860008</v>
+        <v>1028.084755477271</v>
       </c>
       <c r="P40" t="n">
-        <v>70.48841094970703</v>
+        <v>56.62136077880859</v>
       </c>
       <c r="Q40" t="n">
-        <v>465.2996215820312</v>
+        <v>213.0353240966797</v>
       </c>
       <c r="R40" t="n">
-        <v>6.037433155080214</v>
+        <v>5.135922330097087</v>
       </c>
       <c r="S40" t="n">
-        <v>24.16537857055664</v>
+        <v>18.61648178100586</v>
       </c>
       <c r="T40" t="n">
-        <v>15.85715866088867</v>
+        <v>11.53321075439453</v>
       </c>
       <c r="U40" t="n">
-        <v>16.59287261962891</v>
+        <v>11.89191818237305</v>
       </c>
       <c r="V40" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="W40" t="n">
-        <v>1.865290008953964</v>
+        <v>1.145855607589955</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -4071,19 +4071,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack2-5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4092,67 +4092,67 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>39.06799863884642</v>
+        <v>43.54597794064011</v>
       </c>
       <c r="G41" t="n">
-        <v>7.05286614084223</v>
+        <v>7.446103754863215</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04539988977118172</v>
+        <v>0.07202459982808872</v>
       </c>
       <c r="I41" t="n">
-        <v>0.923303130131323</v>
+        <v>1.749091991714451</v>
       </c>
       <c r="J41" t="n">
-        <v>37.10831964367372</v>
+        <v>45.69622759003278</v>
       </c>
       <c r="K41" t="n">
-        <v>10.13989076844286</v>
+        <v>8.436038129159021</v>
       </c>
       <c r="L41" t="n">
-        <v>4.975243003431806</v>
+        <v>5.523639534758232</v>
       </c>
       <c r="M41" t="n">
-        <v>860.5306937032573</v>
+        <v>604.5986794036683</v>
       </c>
       <c r="N41" t="n">
-        <v>1078.027586758422</v>
+        <v>659.9280164809455</v>
       </c>
       <c r="O41" t="n">
-        <v>697.9442014860008</v>
+        <v>1191.173796825068</v>
       </c>
       <c r="P41" t="n">
-        <v>53.71525573730469</v>
+        <v>53.22739791870117</v>
       </c>
       <c r="Q41" t="n">
-        <v>395.3850402832031</v>
+        <v>382.9418029785156</v>
       </c>
       <c r="R41" t="n">
-        <v>7.016949152542373</v>
+        <v>8.531506849315068</v>
       </c>
       <c r="S41" t="n">
-        <v>15.40745544433594</v>
+        <v>23.71091079711914</v>
       </c>
       <c r="T41" t="n">
-        <v>16.68732070922852</v>
+        <v>13.55612564086914</v>
       </c>
       <c r="U41" t="n">
-        <v>16.59346771240234</v>
+        <v>14.23376846313477</v>
       </c>
       <c r="V41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W41" t="n">
-        <v>1.86535690638819</v>
+        <v>1.371506527415863</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -4161,19 +4161,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AB41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack3-3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4182,67 +4182,67 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>11.76508283730059</v>
+        <v>20.31670423759613</v>
       </c>
       <c r="G42" t="n">
-        <v>3.870370617335771</v>
+        <v>5.08606245085487</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0136718921514235</v>
+        <v>0.01335673723064036</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9820330408338379</v>
+        <v>0.454613598426033</v>
       </c>
       <c r="J42" t="n">
-        <v>10.37437249815834</v>
+        <v>20.23299474468698</v>
       </c>
       <c r="K42" t="n">
-        <v>5.169750964649829</v>
+        <v>4.744585803663202</v>
       </c>
       <c r="L42" t="n">
-        <v>2.460458430072616</v>
+        <v>3.972680703054632</v>
       </c>
       <c r="M42" t="n">
-        <v>860.5306937032574</v>
+        <v>1521.082872768478</v>
       </c>
       <c r="N42" t="n">
-        <v>1078.027586758422</v>
+        <v>2424.247785172735</v>
       </c>
       <c r="O42" t="n">
-        <v>89.80293857231344</v>
+        <v>42.68483930392181</v>
       </c>
       <c r="P42" t="n">
-        <v>51.81481552124023</v>
+        <v>80.46111297607422</v>
       </c>
       <c r="Q42" t="n">
-        <v>395.3850402832031</v>
+        <v>248.7073211669922</v>
       </c>
       <c r="R42" t="n">
-        <v>8.728395061728396</v>
+        <v>3.15</v>
       </c>
       <c r="S42" t="n">
-        <v>12.75702667236328</v>
+        <v>5.536376953125</v>
       </c>
       <c r="T42" t="n">
-        <v>12.99042510986328</v>
+        <v>12.17820358276367</v>
       </c>
       <c r="U42" t="n">
-        <v>12.96378707885742</v>
+        <v>9.916950225830078</v>
       </c>
       <c r="V42" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W42" t="n">
-        <v>1.457325869409347</v>
+        <v>1.114815294468783</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -4251,10 +4251,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="b">
         <v>0</v>
@@ -4263,7 +4263,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4275,64 +4275,64 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>74.30702352640125</v>
+        <v>191.7018892014548</v>
       </c>
       <c r="G43" t="n">
-        <v>9.726800131871743</v>
+        <v>15.6231375252134</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07153680202023577</v>
+        <v>0.1791931245776498</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9923624539285906</v>
+        <v>1.319870030007366</v>
       </c>
       <c r="J43" t="n">
-        <v>73.43493900121265</v>
+        <v>195.2420443637932</v>
       </c>
       <c r="K43" t="n">
-        <v>11.19796693881921</v>
+        <v>15.5637945658066</v>
       </c>
       <c r="L43" t="n">
-        <v>10.14950650649157</v>
+        <v>11.79307234343712</v>
       </c>
       <c r="M43" t="n">
-        <v>1038.724424742692</v>
+        <v>1069.806052287372</v>
       </c>
       <c r="N43" t="n">
-        <v>870.2920866533983</v>
+        <v>1261.399773253395</v>
       </c>
       <c r="O43" t="n">
-        <v>1837.017385631282</v>
+        <v>991.8732603692565</v>
       </c>
       <c r="P43" t="n">
-        <v>60.61447525024414</v>
+        <v>85.65777587890625</v>
       </c>
       <c r="Q43" t="n">
-        <v>325.2887878417969</v>
+        <v>382.922607421875</v>
       </c>
       <c r="R43" t="n">
-        <v>6.485526315789474</v>
+        <v>5.450116009280743</v>
       </c>
       <c r="S43" t="n">
-        <v>36.45864868164062</v>
+        <v>20.86791229248047</v>
       </c>
       <c r="T43" t="n">
-        <v>36.7392463684082</v>
+        <v>15.81058120727539</v>
       </c>
       <c r="U43" t="n">
-        <v>36.71780014038086</v>
+        <v>16.97013854980469</v>
       </c>
       <c r="V43" t="n">
         <v>27</v>
       </c>
       <c r="W43" t="n">
-        <v>4.127636445036039</v>
+        <v>1.907700409275072</v>
       </c>
       <c r="X43" t="n">
         <v>1</v>
@@ -4341,19 +4341,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4365,64 +4365,64 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F44" t="n">
-        <v>61.07631869206095</v>
+        <v>63.84750006743872</v>
       </c>
       <c r="G44" t="n">
-        <v>8.818434339812221</v>
+        <v>9.016272063238993</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1082774096668362</v>
+        <v>0.0512157028100285</v>
       </c>
       <c r="I44" t="n">
-        <v>1.399061034005007</v>
+        <v>0.8706627243239781</v>
       </c>
       <c r="J44" t="n">
-        <v>64.70728907990018</v>
+        <v>57.96537894750909</v>
       </c>
       <c r="K44" t="n">
-        <v>9.668957909164302</v>
+        <v>11.0397205698286</v>
       </c>
       <c r="L44" t="n">
-        <v>8.664536066849045</v>
+        <v>8.922291093832561</v>
       </c>
       <c r="M44" t="n">
-        <v>564.0725879940194</v>
+        <v>1246.6391470652</v>
       </c>
       <c r="N44" t="n">
-        <v>688.253801386673</v>
+        <v>1207.06291439684</v>
       </c>
       <c r="O44" t="n">
-        <v>1003.172188420295</v>
+        <v>873.2345158333562</v>
       </c>
       <c r="P44" t="n">
-        <v>76.38814544677734</v>
+        <v>62.89115524291992</v>
       </c>
       <c r="Q44" t="n">
-        <v>341.6778869628906</v>
+        <v>140.3150024414062</v>
       </c>
       <c r="R44" t="n">
-        <v>6.996175908221797</v>
+        <v>6.031292517006802</v>
       </c>
       <c r="S44" t="n">
-        <v>21.95692825317383</v>
+        <v>14.10186386108398</v>
       </c>
       <c r="T44" t="n">
-        <v>15.69404602050781</v>
+        <v>16.19670104980469</v>
       </c>
       <c r="U44" t="n">
-        <v>16.27879333496094</v>
+        <v>15.95381164550781</v>
       </c>
       <c r="V44" t="n">
         <v>27</v>
       </c>
       <c r="W44" t="n">
-        <v>1.829982743892607</v>
+        <v>1.793449883529852</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
@@ -4431,19 +4431,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4455,64 +4455,64 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>51.48332232385754</v>
+        <v>44.7169129072058</v>
       </c>
       <c r="G45" t="n">
-        <v>8.096332618975213</v>
+        <v>7.545551128442019</v>
       </c>
       <c r="H45" t="n">
-        <v>0.07706198393563363</v>
+        <v>0.0530067914210163</v>
       </c>
       <c r="I45" t="n">
-        <v>1.36944448550374</v>
+        <v>0.9948678727591906</v>
       </c>
       <c r="J45" t="n">
-        <v>46.74022424476337</v>
+        <v>44.04273805548605</v>
       </c>
       <c r="K45" t="n">
-        <v>10.12527966041368</v>
+        <v>10.13660723658315</v>
       </c>
       <c r="L45" t="n">
-        <v>7.260491839090461</v>
+        <v>6.705652783707531</v>
       </c>
       <c r="M45" t="n">
-        <v>668.0767830589364</v>
+        <v>843.6072380241505</v>
       </c>
       <c r="N45" t="n">
-        <v>709.4392914823695</v>
+        <v>1055.58666021261</v>
       </c>
       <c r="O45" t="n">
-        <v>1003.172188420295</v>
+        <v>873.2345158333562</v>
       </c>
       <c r="P45" t="n">
-        <v>65.58424377441406</v>
+        <v>54.03067398071289</v>
       </c>
       <c r="Q45" t="n">
-        <v>364.9579467773438</v>
+        <v>199.688720703125</v>
       </c>
       <c r="R45" t="n">
-        <v>5.135667396061269</v>
+        <v>7.288343558282208</v>
       </c>
       <c r="S45" t="n">
-        <v>21.55858993530273</v>
+        <v>15.87891387939453</v>
       </c>
       <c r="T45" t="n">
-        <v>15.74258041381836</v>
+        <v>15.9608268737793</v>
       </c>
       <c r="U45" t="n">
-        <v>16.27884292602539</v>
+        <v>15.953857421875</v>
       </c>
       <c r="V45" t="n">
         <v>27</v>
       </c>
       <c r="W45" t="n">
-        <v>1.829988318678793</v>
+        <v>1.793455029486331</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -4521,19 +4521,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4545,64 +4545,64 @@
         <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F46" t="n">
-        <v>25.3555773977323</v>
+        <v>42.18874107495716</v>
       </c>
       <c r="G46" t="n">
-        <v>5.681876786976805</v>
+        <v>7.329145480833909</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1769491390403922</v>
+        <v>0.0444072346769803</v>
       </c>
       <c r="I46" t="n">
-        <v>1.032525165033017</v>
+        <v>2.063284211666092</v>
       </c>
       <c r="J46" t="n">
-        <v>24.26143466702454</v>
+        <v>40.00093001435103</v>
       </c>
       <c r="K46" t="n">
-        <v>6.366810804772977</v>
+        <v>7.258418084347448</v>
       </c>
       <c r="L46" t="n">
-        <v>3.295255642671946</v>
+        <v>6.720557421751721</v>
       </c>
       <c r="M46" t="n">
-        <v>143.2930249632036</v>
+        <v>950.0420681863994</v>
       </c>
       <c r="N46" t="n">
-        <v>69.8728849267323</v>
+        <v>1529.906244021815</v>
       </c>
       <c r="O46" t="n">
-        <v>1837.017385631282</v>
+        <v>1178.580199934848</v>
       </c>
       <c r="P46" t="n">
-        <v>46.13983154296875</v>
+        <v>95.55585479736328</v>
       </c>
       <c r="Q46" t="n">
-        <v>319.1098022460938</v>
+        <v>81.48159027099609</v>
       </c>
       <c r="R46" t="n">
-        <v>8.021186440677965</v>
+        <v>6.572207084468665</v>
       </c>
       <c r="S46" t="n">
-        <v>37.87921905517578</v>
+        <v>13.375</v>
       </c>
       <c r="T46" t="n">
-        <v>36.68600082397461</v>
+        <v>6.482383728027344</v>
       </c>
       <c r="U46" t="n">
-        <v>36.71780014038086</v>
+        <v>6.947479248046875</v>
       </c>
       <c r="V46" t="n">
         <v>27</v>
       </c>
       <c r="W46" t="n">
-        <v>4.127636445036039</v>
+        <v>0.7810018148073182</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -4611,10 +4611,10 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB46" t="b">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4635,64 +4635,64 @@
         <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>2.349051322706323</v>
+        <v>37.65951740896895</v>
       </c>
       <c r="G47" t="n">
-        <v>1.729423324892472</v>
+        <v>6.924564015210024</v>
       </c>
       <c r="H47" t="n">
-        <v>0.002302754161206277</v>
+        <v>0.03020883589098404</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1085224688878231</v>
+        <v>1.729052710676868</v>
       </c>
       <c r="J47" t="n">
-        <v>1.939574645550133</v>
+        <v>28.95109600971556</v>
       </c>
       <c r="K47" t="n">
-        <v>2.614577182574465</v>
+        <v>9.415038539111737</v>
       </c>
       <c r="L47" t="n">
-        <v>1.120650770156682</v>
+        <v>9.403787349718531</v>
       </c>
       <c r="M47" t="n">
-        <v>1020.105125540537</v>
+        <v>1246.6391470652</v>
       </c>
       <c r="N47" t="n">
-        <v>1239.861191656104</v>
+        <v>1207.06291439684</v>
       </c>
       <c r="O47" t="n">
-        <v>1837.017385631282</v>
+        <v>991.8732603692565</v>
       </c>
       <c r="P47" t="n">
-        <v>90.82353210449219</v>
+        <v>67.49407958984375</v>
       </c>
       <c r="Q47" t="n">
-        <v>335.6142883300781</v>
+        <v>140.3150024414062</v>
       </c>
       <c r="R47" t="n">
-        <v>5.588235294117647</v>
+        <v>5.14792899408284</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>28.15879058837891</v>
       </c>
       <c r="T47" t="n">
-        <v>36.85872650146484</v>
+        <v>16.28567504882812</v>
       </c>
       <c r="U47" t="n">
-        <v>36.71676254272461</v>
+        <v>16.96840286254883</v>
       </c>
       <c r="V47" t="n">
         <v>27</v>
       </c>
       <c r="W47" t="n">
-        <v>4.12751980335585</v>
+        <v>1.907505291758579</v>
       </c>
       <c r="X47" t="n">
         <v>1</v>
@@ -4701,19 +4701,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4725,64 +4725,64 @@
         <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F48" t="n">
-        <v>1.924184753821921</v>
+        <v>18.33543860404358</v>
       </c>
       <c r="G48" t="n">
-        <v>1.565231011685676</v>
+        <v>4.831708341853012</v>
       </c>
       <c r="H48" t="n">
-        <v>0.005546311017555212</v>
+        <v>0.079058844163036</v>
       </c>
       <c r="I48" t="n">
-        <v>1.026207651794815</v>
+        <v>1.203473113403255</v>
       </c>
       <c r="J48" t="n">
-        <v>1.46496651424332</v>
+        <v>17.81690223657325</v>
       </c>
       <c r="K48" t="n">
-        <v>1.067241165458817</v>
+        <v>6.064655033865932</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5593994051982953</v>
+        <v>3.650683724388564</v>
       </c>
       <c r="M48" t="n">
-        <v>346.9305539720874</v>
+        <v>231.9214099087009</v>
       </c>
       <c r="N48" t="n">
-        <v>258.1098876659022</v>
+        <v>126.9167786288484</v>
       </c>
       <c r="O48" t="n">
-        <v>1837.017385631282</v>
+        <v>873.2345158333562</v>
       </c>
       <c r="P48" t="n">
-        <v>109.1999969482422</v>
+        <v>49.04026794433594</v>
       </c>
       <c r="Q48" t="n">
-        <v>334.6475524902344</v>
+        <v>202.6515655517578</v>
       </c>
       <c r="R48" t="n">
-        <v>8.4</v>
+        <v>9.63758389261745</v>
       </c>
       <c r="S48" t="n">
-        <v>37.67742156982422</v>
+        <v>19.03179168701172</v>
       </c>
       <c r="T48" t="n">
-        <v>36.71520233154297</v>
+        <v>15.81405639648438</v>
       </c>
       <c r="U48" t="n">
-        <v>36.71780014038086</v>
+        <v>15.92612075805664</v>
       </c>
       <c r="V48" t="n">
         <v>27</v>
       </c>
       <c r="W48" t="n">
-        <v>4.127636445036039</v>
+        <v>1.790337008689805</v>
       </c>
       <c r="X48" t="n">
         <v>1</v>
@@ -4791,19 +4791,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AB48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4812,67 +4812,67 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
         <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F49" t="n">
-        <v>102.8147780681782</v>
+        <v>12.96274146830324</v>
       </c>
       <c r="G49" t="n">
-        <v>11.44149645892415</v>
+        <v>4.062594619897736</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06440476507917225</v>
+        <v>0.01211690795783718</v>
       </c>
       <c r="I49" t="n">
-        <v>1.21841813162601</v>
+        <v>1.23681502992519</v>
       </c>
       <c r="J49" t="n">
-        <v>101.8263609403926</v>
+        <v>11.04705230605245</v>
       </c>
       <c r="K49" t="n">
-        <v>11.68995147225288</v>
+        <v>9.272378767530702</v>
       </c>
       <c r="L49" t="n">
-        <v>9.801789209002013</v>
+        <v>1.784445470901258</v>
       </c>
       <c r="M49" t="n">
-        <v>1596.384645480638</v>
+        <v>1069.806052287372</v>
       </c>
       <c r="N49" t="n">
-        <v>2062.878249484846</v>
+        <v>1261.399773253395</v>
       </c>
       <c r="O49" t="n">
-        <v>701.1612573894214</v>
+        <v>873.2345158333562</v>
       </c>
       <c r="P49" t="n">
-        <v>66.01976013183594</v>
+        <v>105.0299987792969</v>
       </c>
       <c r="Q49" t="n">
-        <v>454.6460571289062</v>
+        <v>382.922607421875</v>
       </c>
       <c r="R49" t="n">
-        <v>7.43298969072165</v>
+        <v>5.26</v>
       </c>
       <c r="S49" t="n">
-        <v>18.416015625</v>
+        <v>19.58560180664062</v>
       </c>
       <c r="T49" t="n">
-        <v>15.11469268798828</v>
+        <v>15.83551406860352</v>
       </c>
       <c r="U49" t="n">
-        <v>15.6436767578125</v>
+        <v>15.95330810546875</v>
       </c>
       <c r="V49" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W49" t="n">
-        <v>1.507359406730047</v>
+        <v>1.793393278008584</v>
       </c>
       <c r="X49" t="n">
         <v>1</v>
@@ -4881,19 +4881,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z49" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4902,67 +4902,67 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>88.05334269004298</v>
+        <v>2.85732303769013</v>
       </c>
       <c r="G50" t="n">
-        <v>10.58834255013879</v>
+        <v>1.907369047580953</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05515797395027684</v>
+        <v>0.02887294462951255</v>
       </c>
       <c r="I50" t="n">
-        <v>1.649878582129222</v>
+        <v>0.578733843026882</v>
       </c>
       <c r="J50" t="n">
-        <v>85.39405070867369</v>
+        <v>0.7100024657034401</v>
       </c>
       <c r="K50" t="n">
-        <v>11.5906532143797</v>
+        <v>2.186725428497687</v>
       </c>
       <c r="L50" t="n">
-        <v>7.89223738371803</v>
+        <v>1.36933897928384</v>
       </c>
       <c r="M50" t="n">
-        <v>1596.384645480638</v>
+        <v>98.96195467259375</v>
       </c>
       <c r="N50" t="n">
-        <v>2062.878249484846</v>
+        <v>27.93346101506648</v>
       </c>
       <c r="O50" t="n">
-        <v>219.6621463811197</v>
+        <v>991.8732603692565</v>
       </c>
       <c r="P50" t="n">
-        <v>87.84720611572266</v>
+        <v>124.529411315918</v>
       </c>
       <c r="Q50" t="n">
-        <v>454.6460571289062</v>
+        <v>419.0769348144531</v>
       </c>
       <c r="R50" t="n">
-        <v>5.498627630375115</v>
+        <v>5.352941176470588</v>
       </c>
       <c r="S50" t="n">
-        <v>14.58658218383789</v>
+        <v>9.847328186035156</v>
       </c>
       <c r="T50" t="n">
-        <v>8.84100341796875</v>
+        <v>17.01529693603516</v>
       </c>
       <c r="U50" t="n">
-        <v>10.71795654296875</v>
+        <v>16.97539901733398</v>
       </c>
       <c r="V50" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W50" t="n">
-        <v>1.032737563303303</v>
+        <v>1.908291765440442</v>
       </c>
       <c r="X50" t="n">
         <v>1</v>
@@ -4971,19 +4971,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4992,67 +4992,67 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>29.21169683300565</v>
+        <v>69.20216447183583</v>
       </c>
       <c r="G51" t="n">
-        <v>6.098646372482808</v>
+        <v>9.386742373518521</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03591037042181564</v>
+        <v>0.07607741432415248</v>
       </c>
       <c r="I51" t="n">
-        <v>2.678023626602801</v>
+        <v>0.7900956747275985</v>
       </c>
       <c r="J51" t="n">
-        <v>27.04120509694764</v>
+        <v>68.46786923647588</v>
       </c>
       <c r="K51" t="n">
-        <v>7.593867191884467</v>
+        <v>10.55774251794342</v>
       </c>
       <c r="L51" t="n">
-        <v>3.276829279489634</v>
+        <v>8.108088110730542</v>
       </c>
       <c r="M51" t="n">
-        <v>813.4613062988476</v>
+        <v>909.6282396898714</v>
       </c>
       <c r="N51" t="n">
-        <v>1187.603649420052</v>
+        <v>1376.742997107743</v>
       </c>
       <c r="O51" t="n">
-        <v>230.6472153196289</v>
+        <v>1200.746499757197</v>
       </c>
       <c r="P51" t="n">
-        <v>73.69647979736328</v>
+        <v>57.98098754882812</v>
       </c>
       <c r="Q51" t="n">
-        <v>555.2509155273438</v>
+        <v>226.8989715576172</v>
       </c>
       <c r="R51" t="n">
-        <v>9.409214092140921</v>
+        <v>6.835234474017744</v>
       </c>
       <c r="S51" t="n">
-        <v>15.18545150756836</v>
+        <v>43.94636535644531</v>
       </c>
       <c r="T51" t="n">
-        <v>5.670394897460938</v>
+        <v>55.62157440185547</v>
       </c>
       <c r="U51" t="n">
-        <v>6.852359771728516</v>
+        <v>54.34227752685547</v>
       </c>
       <c r="V51" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W51" t="n">
-        <v>0.6602647906960375</v>
+        <v>6.108894442710066</v>
       </c>
       <c r="X51" t="n">
         <v>1</v>
@@ -5061,19 +5061,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z51" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA51" t="n">
         <v>7</v>
       </c>
       <c r="AB51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5082,67 +5082,67 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F52" t="n">
-        <v>12.13484986779408</v>
+        <v>61.18569229561592</v>
       </c>
       <c r="G52" t="n">
-        <v>3.930721399577905</v>
+        <v>8.826326699299985</v>
       </c>
       <c r="H52" t="n">
-        <v>0.007601457394461801</v>
+        <v>0.108414990679129</v>
       </c>
       <c r="I52" t="n">
-        <v>2.330395917055725</v>
+        <v>1.374906561918302</v>
       </c>
       <c r="J52" t="n">
-        <v>10.49779885912698</v>
+        <v>64.82498624709849</v>
       </c>
       <c r="K52" t="n">
-        <v>3.969444551953554</v>
+        <v>9.671016860040778</v>
       </c>
       <c r="L52" t="n">
-        <v>3.154767028811903</v>
+        <v>8.688621115097899</v>
       </c>
       <c r="M52" t="n">
-        <v>1596.384645480638</v>
+        <v>564.3656095189313</v>
       </c>
       <c r="N52" t="n">
-        <v>2062.878249484846</v>
+        <v>688.9992167789289</v>
       </c>
       <c r="O52" t="n">
-        <v>104.7112464174332</v>
+        <v>1069.631855498276</v>
       </c>
       <c r="P52" t="n">
-        <v>58.30434799194336</v>
+        <v>72.80867767333984</v>
       </c>
       <c r="Q52" t="n">
-        <v>454.6460571289062</v>
+        <v>233.2991180419922</v>
       </c>
       <c r="R52" t="n">
-        <v>3.326086956521739</v>
+        <v>7.055226824457594</v>
       </c>
       <c r="S52" t="n">
-        <v>36.37816619873047</v>
+        <v>21.47043228149414</v>
       </c>
       <c r="T52" t="n">
-        <v>15.61029434204102</v>
+        <v>15.61592102050781</v>
       </c>
       <c r="U52" t="n">
-        <v>17.57995986938477</v>
+        <v>16.19664001464844</v>
       </c>
       <c r="V52" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W52" t="n">
-        <v>1.693931566683645</v>
+        <v>1.820747467331753</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
@@ -5151,19 +5151,19 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA52" t="n">
         <v>7</v>
       </c>
       <c r="AB52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5172,67 +5172,67 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
         <v>5</v>
-      </c>
-      <c r="D53" t="n">
-        <v>7</v>
       </c>
       <c r="E53" t="n">
         <v>17</v>
       </c>
       <c r="F53" t="n">
-        <v>10.66095440926927</v>
+        <v>51.48332232385754</v>
       </c>
       <c r="G53" t="n">
-        <v>3.684284019792765</v>
+        <v>8.096332618975213</v>
       </c>
       <c r="H53" t="n">
-        <v>0.006678186513162986</v>
+        <v>0.07516933218822384</v>
       </c>
       <c r="I53" t="n">
-        <v>1.109057888352315</v>
+        <v>1.382210806497017</v>
       </c>
       <c r="J53" t="n">
-        <v>6.670378108564028</v>
+        <v>46.74022424476337</v>
       </c>
       <c r="K53" t="n">
-        <v>9.113344215280192</v>
+        <v>10.12527966041368</v>
       </c>
       <c r="L53" t="n">
-        <v>4.656825247235423</v>
+        <v>7.260491839090461</v>
       </c>
       <c r="M53" t="n">
-        <v>1596.384645480638</v>
+        <v>684.8979607127999</v>
       </c>
       <c r="N53" t="n">
-        <v>2062.878249484846</v>
+        <v>735.9996188801223</v>
       </c>
       <c r="O53" t="n">
-        <v>379.5341318254959</v>
+        <v>1069.631855498276</v>
       </c>
       <c r="P53" t="n">
-        <v>146.5743255615234</v>
+        <v>65.58424377441406</v>
       </c>
       <c r="Q53" t="n">
-        <v>454.6460571289062</v>
+        <v>195.0476684570312</v>
       </c>
       <c r="R53" t="n">
-        <v>4.412162162162162</v>
+        <v>5.135667396061269</v>
       </c>
       <c r="S53" t="n">
-        <v>17.78348922729492</v>
+        <v>21.55858993530273</v>
       </c>
       <c r="T53" t="n">
-        <v>16.03477096557617</v>
+        <v>15.5971794128418</v>
       </c>
       <c r="U53" t="n">
-        <v>16.12677383422852</v>
+        <v>16.19669342041016</v>
       </c>
       <c r="V53" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W53" t="n">
-        <v>1.55390862490766</v>
+        <v>1.820753470947645</v>
       </c>
       <c r="X53" t="n">
         <v>1</v>
@@ -5241,13 +5241,733 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="Z53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA53" t="n">
         <v>7</v>
       </c>
       <c r="AB53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6_stack4-5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>39.1195777863611</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7.057520344351704</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.07108994774088356</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9322188025795687</v>
+      </c>
+      <c r="J54" t="n">
+        <v>36.79064106863132</v>
+      </c>
+      <c r="K54" t="n">
+        <v>8.840774817367098</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5.671762440068829</v>
+      </c>
+      <c r="M54" t="n">
+        <v>550.2828322359784</v>
+      </c>
+      <c r="N54" t="n">
+        <v>686.8806677693593</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1200.746499757197</v>
+      </c>
+      <c r="P54" t="n">
+        <v>79.11206817626953</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>142.9230346679688</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4.830459770114943</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50.87718963623047</v>
+      </c>
+      <c r="T54" t="n">
+        <v>54.57644653320312</v>
+      </c>
+      <c r="U54" t="n">
+        <v>54.34227752685547</v>
+      </c>
+      <c r="V54" t="n">
+        <v>27</v>
+      </c>
+      <c r="W54" t="n">
+        <v>6.108894442710066</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="n">
+        <v>14</v>
+      </c>
+      <c r="F55" t="n">
+        <v>161.3021873172543</v>
+      </c>
+      <c r="G55" t="n">
+        <v>14.33095682585803</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1575366737432416</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.29758281022131</v>
+      </c>
+      <c r="J55" t="n">
+        <v>167.3472753636751</v>
+      </c>
+      <c r="K55" t="n">
+        <v>14.58396893756067</v>
+      </c>
+      <c r="L55" t="n">
+        <v>11.86991122183367</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1023.902457025022</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1319.071385180569</v>
+      </c>
+      <c r="O55" t="n">
+        <v>960.7227434507695</v>
+      </c>
+      <c r="P55" t="n">
+        <v>82.21251678466797</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>378.6636047363281</v>
+      </c>
+      <c r="R55" t="n">
+        <v>5.999532928538066</v>
+      </c>
+      <c r="S55" t="n">
+        <v>18.13150024414062</v>
+      </c>
+      <c r="T55" t="n">
+        <v>13.97328948974609</v>
+      </c>
+      <c r="U55" t="n">
+        <v>14.97057342529297</v>
+      </c>
+      <c r="V55" t="n">
+        <v>30</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.442501978666151</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>24</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" t="n">
+        <v>95.50236520524766</v>
+      </c>
+      <c r="G56" t="n">
+        <v>11.02712056681438</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.06882390132614877</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.041021374008428</v>
+      </c>
+      <c r="J56" t="n">
+        <v>78.38602474517323</v>
+      </c>
+      <c r="K56" t="n">
+        <v>11.87045935674072</v>
+      </c>
+      <c r="L56" t="n">
+        <v>10.23217610367177</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1387.633705225059</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1366.267949227093</v>
+      </c>
+      <c r="O56" t="n">
+        <v>722.8960009320434</v>
+      </c>
+      <c r="P56" t="n">
+        <v>67.45973205566406</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>151.3825378417969</v>
+      </c>
+      <c r="R56" t="n">
+        <v>5.915837104072398</v>
+      </c>
+      <c r="S56" t="n">
+        <v>16.70909118652344</v>
+      </c>
+      <c r="T56" t="n">
+        <v>16.0506706237793</v>
+      </c>
+      <c r="U56" t="n">
+        <v>16.17555999755859</v>
+      </c>
+      <c r="V56" t="n">
+        <v>30</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.558609456007173</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>26</v>
+      </c>
+      <c r="E57" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" t="n">
+        <v>44.23710646893255</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7.504960579570328</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.04789549974336052</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.04316809888089</v>
+      </c>
+      <c r="J57" t="n">
+        <v>43.80161452731908</v>
+      </c>
+      <c r="K57" t="n">
+        <v>8.341678666274161</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6.116589750012188</v>
+      </c>
+      <c r="M57" t="n">
+        <v>923.6171812794349</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1462.308837660917</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1270.148596015136</v>
+      </c>
+      <c r="P57" t="n">
+        <v>118.0050659179688</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>84.08098602294922</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7.141772151898734</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5.820903778076172</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5.580024719238281</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5.596988677978516</v>
+      </c>
+      <c r="V57" t="n">
+        <v>30</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.5393024711341715</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB57" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" t="n">
+        <v>28.69487126960873</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6.044455710115736</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.02067899558908072</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.677204422420961</v>
+      </c>
+      <c r="J58" t="n">
+        <v>28.69938606133417</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10.54850864160926</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5.447419924509113</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1387.633705225059</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1366.267949227093</v>
+      </c>
+      <c r="O58" t="n">
+        <v>960.7227434507695</v>
+      </c>
+      <c r="P58" t="n">
+        <v>63.78455352783203</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>151.3825378417969</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4.796747967479675</v>
+      </c>
+      <c r="S58" t="n">
+        <v>24.12905883789062</v>
+      </c>
+      <c r="T58" t="n">
+        <v>14.386474609375</v>
+      </c>
+      <c r="U58" t="n">
+        <v>14.97392272949219</v>
+      </c>
+      <c r="V58" t="n">
+        <v>30</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.442824703641159</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>28</v>
+      </c>
+      <c r="F59" t="n">
+        <v>28.08281634949455</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5.979644830900212</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.03372199043970103</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.609492680108303</v>
+      </c>
+      <c r="J59" t="n">
+        <v>27.16081199540273</v>
+      </c>
+      <c r="K59" t="n">
+        <v>8.328191936372214</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3.272904793903614</v>
+      </c>
+      <c r="M59" t="n">
+        <v>832.7745777554263</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1228.523031215999</v>
+      </c>
+      <c r="O59" t="n">
+        <v>306.6795853297397</v>
+      </c>
+      <c r="P59" t="n">
+        <v>73.40171051025391</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>476.6447143554688</v>
+      </c>
+      <c r="R59" t="n">
+        <v>9.33048433048433</v>
+      </c>
+      <c r="S59" t="n">
+        <v>14.81626510620117</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5.677833557128906</v>
+      </c>
+      <c r="U59" t="n">
+        <v>6.881149291992188</v>
+      </c>
+      <c r="V59" t="n">
+        <v>30</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.6630388287215303</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>21</v>
+      </c>
+      <c r="E60" t="n">
+        <v>18</v>
+      </c>
+      <c r="F60" t="n">
+        <v>27.47165958082578</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5.914220433650573</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.03834655752598065</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.526144806288355</v>
+      </c>
+      <c r="J60" t="n">
+        <v>25.50437496566868</v>
+      </c>
+      <c r="K60" t="n">
+        <v>9.303180074604064</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.923677162534643</v>
+      </c>
+      <c r="M60" t="n">
+        <v>716.4048444821444</v>
+      </c>
+      <c r="N60" t="n">
+        <v>907.4843914880655</v>
+      </c>
+      <c r="O60" t="n">
+        <v>722.8960009320434</v>
+      </c>
+      <c r="P60" t="n">
+        <v>51.26511764526367</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>192.9559326171875</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="S60" t="n">
+        <v>23.83240127563477</v>
+      </c>
+      <c r="T60" t="n">
+        <v>15.61608123779297</v>
+      </c>
+      <c r="U60" t="n">
+        <v>16.19084167480469</v>
+      </c>
+      <c r="V60" t="n">
+        <v>30</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.560081934651685</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6_stackf1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>18</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4.778121649761839</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.466514430128473</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.004666578947026663</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.41228867138329</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.961433531746032</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.367708189432491</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.498564076360232</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1023.902457025022</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1319.071385180569</v>
+      </c>
+      <c r="O61" t="n">
+        <v>722.8960009320434</v>
+      </c>
+      <c r="P61" t="n">
+        <v>82.72972869873047</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>378.6636047363281</v>
+      </c>
+      <c r="R61" t="n">
+        <v>3.027027027027027</v>
+      </c>
+      <c r="S61" t="n">
+        <v>22.73488235473633</v>
+      </c>
+      <c r="T61" t="n">
+        <v>16.097900390625</v>
+      </c>
+      <c r="U61" t="n">
+        <v>16.19084167480469</v>
+      </c>
+      <c r="V61" t="n">
+        <v>30</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.560081934651685</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.1980716765873016</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB61" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results/synapse_table.xlsx
+++ b/results/synapse_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB61"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,125 +446,130 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Curated</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>T_Cell</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tumour_Cell</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Contact_Area_um2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Contact_Diameter_um</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Contact_Fraction_T</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mCherry_Enrichment</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Contact_Area_Voxelface_um2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Contact_Length_um</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Contact_Width_um</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>T_Surface_um2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>T_Volume_um3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tumour_Volume_um3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>GFP_IS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DAPI_T</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Z_Contact</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mCherry_IS</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mCherry_TumourSurface</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mCherry_TumourMean</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mCherry_Background</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mCherry_SNR</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Voxel_Z_um</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Voxel_XY_um</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>N_T_Cells</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>N_Tumour_Cells</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Clipped_Z</t>
         </is>
@@ -584,79 +589,82 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>84.5608327264332</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>10.37623227202582</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.07737796324921047</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.6253241477476021</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>83.62755543676845</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>14.03104424429663</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>12.86208212821971</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1092.828360628839</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1592.834996083847</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1285.802319252512</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>88.45500946044922</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>204.0211181640625</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>7.780205655526992</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>9.800426483154297</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>15.67255401611328</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>15.13949584960938</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>34</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1.458778638510444</v>
       </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
       <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>15</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="b">
+      <c r="AC2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -674,79 +682,82 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>18</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>34.92478816276656</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>6.668404710298625</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.03195816417380496</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.3860645935959985</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>31.90394581328354</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>9.536226166289516</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>5.956241320297747</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1092.828360628839</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1592.834996083847</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>613.9084241064048</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>63.61301422119141</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>204.0211181640625</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>11.39383561643836</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>5.980472564697266</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>15.49085998535156</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>14.75030136108398</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>34</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.421277481818923</v>
       </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
       <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>15</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="b">
+      <c r="AC3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -764,79 +775,82 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>52.20913307181591</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>8.153203837963112</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.02701226426312793</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.226646619458725</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>42.2526198377775</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7.399741764770707</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>7.099908920263616</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1932.793658585742</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2400.394492620544</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>118.2071882561732</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>70.91806030273438</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>107.1266098022461</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>8.061872909698996</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>19.00606918334961</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>15.49433135986328</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>16.54124450683594</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>35</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1.593845289212394</v>
       </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
       <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>15</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="b">
+      <c r="AC4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -854,79 +868,82 @@
       <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>19</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>24.29279287717144</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>5.561523581112946</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.01256874616142257</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1.587181559021662</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>15.93860478784432</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>13.43429924579264</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>9.552122853461727</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1932.793658585742</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2400.394492620544</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1410.129760202998</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>66.36683654785156</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>107.1266098022461</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>8.457286432160805</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>26.67567443847656</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>16.80694580078125</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>17.08962249755859</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>35</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.646684703856187</v>
       </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
       <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>15</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" t="b">
+      <c r="AC5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -944,79 +961,82 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>25</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>165.1605929802871</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>14.50134470366146</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.1464911706149212</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.184387196221472</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>182.2559577863083</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>14.49553247207279</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>11.68787243690289</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1127.444011041743</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1216.63561732897</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>978.926571977442</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>129.6198272705078</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>129.9382019042969</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>6.390368271954674</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>20.3828010559082</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>17.20957565307617</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>17.82429885864258</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>31</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1.71747505199024</v>
       </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
       <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>24</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>3</v>
       </c>
-      <c r="AB6" t="b">
+      <c r="AC6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1034,79 +1054,82 @@
       <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>31</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>28</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>102.6177982639215</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>11.43053099130921</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.06482144253333359</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.9502608405183065</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>92.1352546703428</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>13.03827996704315</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>7.191178629248816</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1583.084150142935</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>1589.696404958558</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>681.9766191360962</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>61.66102981567383</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>255.0967254638672</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>8.965342349957735</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>21.26969146728516</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>22.38300323486328</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>22.13632202148438</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>31</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>2.132963608623924</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>24</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>3</v>
       </c>
-      <c r="AB7" t="b">
+      <c r="AC7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1124,79 +1147,82 @@
       <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>29</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>28</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>78.71812809334939</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>10.011345243072</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.06302329860179971</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.5390552164821399</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>79.49304253137751</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>12.78572213935404</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>6.085695149005605</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1249.032180792605</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1754.237044701801</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>681.9766191360962</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>94.58654022216797</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>80.39250183105469</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>9.191239316239317</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>12.9010124206543</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>23.93263626098633</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>22.13205337524414</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>31</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>2.132552299686528</v>
       </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
       <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>3</v>
       </c>
-      <c r="AB8" t="b">
+      <c r="AC8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1214,79 +1240,82 @@
       <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>22</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>28</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>34.50673131588045</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>6.628373470990467</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.04079112435338021</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.5966055059654756</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>19.39487448817508</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>10.23660256873005</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>6.080637040532735</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>845.9372440176685</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>805.7940390287224</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>681.9766191360962</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>68.32024383544922</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>87.19190979003906</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>8.51963746223565</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>13.78517532348633</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>23.10601425170898</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>22.13089752197266</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>31</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>2.132440926489003</v>
       </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>24</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>3</v>
       </c>
-      <c r="AB9" t="b">
+      <c r="AC9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1304,79 +1333,82 @@
       <c r="C10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>31</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>20</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>4.023872892926404</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>2.263482734694872</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.002541793430603857</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1.299661801906902</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>3.00839780661885</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>6.633177918833388</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1.735099402771775</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1583.084150142935</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>1589.696404958558</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>978.926571977442</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>54.70370483398438</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>255.0967254638672</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>6.481481481481482</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>23.09311676025391</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>17.76855850219727</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>17.82120895385742</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>31</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.717177321660222</v>
       </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
       <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>24</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>3</v>
       </c>
-      <c r="AB10" t="b">
+      <c r="AC10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1394,79 +1426,82 @@
       <c r="C11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>31</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>34</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1.881226390774671</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.547660115572446</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.001188330001664673</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2.248884837781639</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1.147287939200926</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1.031330888391748</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.6450013958335229</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1583.084150142935</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>1589.696404958558</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>423.2782456342025</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>82.18181610107422</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>255.0967254638672</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>8.454545454545455</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>25.59999847412109</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>11.38341903686523</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>11.51303863525391</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>31</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1.109348355605063</v>
       </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
       <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>24</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>3</v>
       </c>
-      <c r="AB11" t="b">
+      <c r="AC11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1484,79 +1519,82 @@
       <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
+      <c r="D12" t="b">
+        <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>125.0273232618309</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>12.61704133897284</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.1652040569927973</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.8132080033893057</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>129.7086337890394</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>12.9276322477163</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>11.51463554650306</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>756.805405010616</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>709.8708477620967</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1349.437254317734</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>85.76812744140625</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>159.6872100830078</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>5.789662598707825</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>17.91007614135742</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>22.02397918701172</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>21.48800277709961</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>30</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>2.070494271861424</v>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
       <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>21</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>4</v>
       </c>
-      <c r="AB12" t="b">
+      <c r="AC12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1574,79 +1612,82 @@
       <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>22</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>70.11060029461055</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>9.448152666009314</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.04371800109338758</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1.604121207104173</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>52.62213510949175</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>11.42570779614305</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>9.941571652976142</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1603.700959356417</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1944.39643450521</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2805.272747782743</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>61.00719451904297</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>256.7391052246094</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>6.670863309352518</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>23.65461349487305</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>14.74615097045898</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>15.18851089477539</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>30</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.463501523708478</v>
       </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
       <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>21</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>4</v>
       </c>
-      <c r="AB13" t="b">
+      <c r="AC13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1664,79 +1705,82 @@
       <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>25</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>18.69172995199843</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>4.878426973358839</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.07529923076635954</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.5334264930008338</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>20.61386024780735</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5.41505701591934</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3.070913304007383</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>248.2326812872183</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>176.271124074008</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>144.8852128211243</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>49.12820434570312</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>220.4149932861328</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>13.37948717948718</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>12.85225677490234</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>24.09377288818359</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>22.90938949584961</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>30</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>2.20745316421638</v>
       </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
       <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>21</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>4</v>
       </c>
-      <c r="AB14" t="b">
+      <c r="AC14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1754,79 +1798,82 @@
       <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>24</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>8.299610212567741</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>3.250752517268741</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.03343480064562755</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.5634359326011884</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>4.036078847364684</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>4.712532271705335</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2.092191005101498</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>248.2326812872182</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>176.271124074008</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1349.437254317734</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>76.14286041259766</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>220.4149932861328</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>11.35714285714286</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>12.1615104675293</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>21.58454895019531</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>21.48779296875</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>30</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>2.070474055604447</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
       <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>21</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>4</v>
       </c>
-      <c r="AB15" t="b">
+      <c r="AC15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1844,79 +1891,82 @@
       <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>105.5476036149093</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>11.59255721463278</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.102003705707875</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1.577234668001973</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>102.293164350068</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>13.96675211202239</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>11.60643684099987</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1034.742834904288</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>1485.495179598985</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>2598.557289793438</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>88.97058868408203</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>365.7790222167969</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>5.770152505446623</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>29.23386383056641</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>18.53488540649414</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>19.37087631225586</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>34</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.866496801098956</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>5</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>6</v>
       </c>
-      <c r="AB16" t="b">
+      <c r="AC16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1934,79 +1984,82 @@
       <c r="C17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>12</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>45.41324545693446</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>7.604073906172495</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.237983525824275</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1.910871585948732</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>47.14400652296509</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7.510745707888075</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>6.113659026114961</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>190.8251644715409</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>130.133834532269</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>2598.557289793438</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>61.47547912597656</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>304.2307739257812</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>10.0319829424307</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>35.80643463134766</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>18.73827362060547</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>19.37454605102539</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>34</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1.866850401811891</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>5</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>6</v>
       </c>
-      <c r="AB17" t="b">
+      <c r="AC17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2024,79 +2077,82 @@
       <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>4</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>9</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>140.6022927638413</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>13.37985049346043</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.1646634703696119</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1.108304360448542</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>132.5928990639677</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>13.85652443028741</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>10.78744456562013</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>853.8766518660045</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>979.0050367555742</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1125.106453637748</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>62.54329299926758</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>251.7646179199219</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>5.990009514747859</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>20.9851188659668</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>18.9344367980957</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>19.37041091918945</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>31</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1.866451957765299</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
       <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>8</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>3</v>
       </c>
-      <c r="AB18" t="b">
+      <c r="AC18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2114,79 +2170,82 @@
       <c r="C19" t="n">
         <v>2</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>9</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>113.7217972777936</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>12.03308312081498</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.05107320861566589</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1.295822360397382</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>102.2023692170689</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>13.23769378265101</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>11.80227140798951</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>2226.642898697992</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3154.362545692942</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1125.106453637748</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>67.34125518798828</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>204.7052154541016</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>6.437262357414449</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>23.91337585449219</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>18.45420837402344</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>19.37316513061523</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>31</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>1.866717342084155</v>
       </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
       <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>8</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>3</v>
       </c>
-      <c r="AB19" t="b">
+      <c r="AC19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2204,79 +2263,82 @@
       <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>16</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>17</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>96.95119108165574</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>11.11044960360917</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.09953188980586478</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>1.53743212489533</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>93.79343563472933</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>12.02014911482921</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>12.00364690355332</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>974.0716394590453</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>1393.259832904573</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>830.1181202497072</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>99.77192687988281</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>229.0110168457031</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>6.473684210526316</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>22.83287048339844</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>14.85130310058594</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>16.25333023071289</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>30</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1.566103071115922</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
       <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>14</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>5</v>
       </c>
-      <c r="AB20" t="b">
+      <c r="AC20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2294,79 +2356,82 @@
       <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>16</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>23</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>10.5198191289849</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>3.659815530663395</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.01079984130820924</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.7160482235605999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>6.401480578871632</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>3.258324042490942</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2.626138457690976</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>974.0716394590453</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>1393.259832904573</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>64.85113912627091</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>57.55339813232422</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>229.0110168457031</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>10.57281553398058</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>10.41498565673828</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>14.54508972167969</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>14.19417190551758</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>30</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>1.367691168371923</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
       <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>14</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>5</v>
       </c>
-      <c r="AB21" t="b">
+      <c r="AC21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2384,79 +2449,82 @@
       <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>8.731901203885307</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>3.334336802650169</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.009947419084446952</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1.276233094488507</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>7.999422110367494</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>4.896207690951348</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>3.237261894490558</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>877.8057031434276</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>1086.541015185767</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>1031.576438104154</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>62.71186447143555</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>344.8912658691406</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>4.47457627118644</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>22.42569351196289</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>17.57178497314453</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>17.64904022216797</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>30</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1.700587861185255</v>
       </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
       <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>14</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>5</v>
       </c>
-      <c r="AB22" t="b">
+      <c r="AC22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2474,79 +2542,82 @@
       <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>15</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>2.085875587474972</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>1.629668458113743</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>0.002376238363461799</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>1.665803333939317</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>1.504198903309425</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2.033988971161878</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.7996796383834807</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>877.8057031434276</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>1086.541015185767</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>329.5520681552786</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>44.875</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>344.8912658691406</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>3.125</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>24.64285659790039</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>14.79337692260742</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>14.93109130859375</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>30</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>1.438697646671471</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
       <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>5</v>
       </c>
-      <c r="AB23" t="b">
+      <c r="AC23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2564,79 +2635,82 @@
       <c r="C24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>16</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>6</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>36.60088930737363</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>6.826543754977513</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0.05304819248859279</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1.014369849598692</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>39.55791534708321</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>7.124096481281727</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>4.603168408349381</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>689.9554459889299</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>860.1701302743434</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>735.9603864910562</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>109.1253814697266</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>190.6574249267578</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>4.051987767584098</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>19.77242660522461</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>19.49232482910156</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>19.50852584838867</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>34</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>1.879760135948815</v>
       </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
       <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>12</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>19</v>
       </c>
-      <c r="AB24" t="b">
+      <c r="AC24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2654,79 +2728,82 @@
       <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>28</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>31</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>7.801744604228981</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>3.151743921708825</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.01096385430290432</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1.236748356448535</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>5.383348194409691</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>8.452171571467112</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>1.791152272582819</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>711.5877672838375</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>736.4311751598494</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>326.2173150846597</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>59.1929817199707</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>263.4835510253906</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>9.105263157894736</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>23.421875</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>18.93827056884766</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>19.05930328369141</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>34</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>1.836474924352145</v>
       </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
       <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>12</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>19</v>
       </c>
-      <c r="AB25" t="b">
+      <c r="AC25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2744,79 +2821,82 @@
       <c r="C26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>28</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>29</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>3.428392670130564</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>2.089297758216958</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>0.004817947732880363</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>1.068101191743832</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>1.741502968962831</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>6.071494920142931</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>0.5197760763066344</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>711.5877672838375</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>736.4311751598494</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>1093.05359177074</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>41.33333206176758</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>263.4835510253906</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>12.22222222222222</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>21.48554992675781</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>20.11565017700195</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>20.12346267700195</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>34</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1.93901288244219</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>12</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>19</v>
       </c>
-      <c r="AB26" t="b">
+      <c r="AC26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2834,79 +2914,82 @@
       <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>11</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>112.0490761363225</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>11.94425864956912</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>0.1107586237662319</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2.033693665917514</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>117.0146931095369</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>11.58079108856258</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>10.12496176282187</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1011.651032905702</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>1403.813345563355</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>946.0105975509803</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>64.20115661621094</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>181.9292144775391</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>6.032976092333058</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>43.02751159667969</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>21.15732192993164</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>24.35424423217773</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>30</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>2.346673336806241</v>
       </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
       <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>7</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>9</v>
       </c>
-      <c r="AB27" t="b">
+      <c r="AC27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2924,79 +3007,82 @@
       <c r="C28" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>7</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>12</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>45.53309471069962</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>7.614101180036566</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.09132810893583294</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>2.492789860365837</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>51.9657709155824</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>6.465727412221991</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>6.403805078529096</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>498.5660520211925</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>522.850049083976</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>194.2003258772178</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>76.60713958740234</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>296.184814453125</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>4.163690476190476</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>15.36088180541992</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>6.162124633789062</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>8.062900543212891</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>30</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>0.7769074474944753</v>
       </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
       <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>7</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>9</v>
       </c>
-      <c r="AB28" t="b">
+      <c r="AC28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3014,79 +3100,82 @@
       <c r="C29" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>23.04820429852552</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>5.41718424534533</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.0227827615935167</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>2.031709996662402</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>24.3140351748881</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5.211333148845979</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>4.347343405962934</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>1011.651032905702</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>1403.813345563355</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>91.80379041468477</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>44.7634391784668</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>181.9292144775391</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>2.510752688172043</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>57.79798126220703</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>28.44794845581055</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>33.1793212890625</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>30</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>3.197020932371934</v>
       </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
       <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>7</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>9</v>
       </c>
-      <c r="AB29" t="b">
+      <c r="AC29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3104,79 +3193,82 @@
       <c r="C30" t="n">
         <v>4</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>14</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>21.58992608551589</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>5.243009408725876</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>0.02134127815152276</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>2.587593449478455</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>20.53348573841836</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>4.897820056941097</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2.819530846696294</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>1011.651032905702</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>1403.813345563355</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>168.5031110389193</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>45.51694869995117</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>181.9292144775391</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>3.957627118644068</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>51.13585662841797</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>19.76193618774414</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>22.55403137207031</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>30</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>2.173212338422715</v>
       </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
       <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>7</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>9</v>
       </c>
-      <c r="AB30" t="b">
+      <c r="AC30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3194,79 +3286,82 @@
       <c r="C31" t="n">
         <v>5</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>7</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>6</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>9.921895122498064</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>3.554286036418491</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>0.0199008638519903</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1.362596109405644</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>6.915321099244549</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5.365853976173806</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>1.69332527090525</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>498.5660520211925</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>522.850049083976</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>235.158940062231</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>66.80999755859375</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>296.184814453125</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>5.15</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>7.163978576660156</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>5.257595062255859</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>5.348758697509766</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>30</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>0.5153840661527388</v>
       </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
       <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>7</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>9</v>
       </c>
-      <c r="AB31" t="b">
+      <c r="AC31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3284,79 +3379,82 @@
       <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>18</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>193.9078911847606</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>15.71277171897562</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.2385338574566688</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>1.17553765042985</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>183.345910803501</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>13.13459811537022</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>12.49634604136964</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>812.9155888068642</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>900.1479347327039</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1224.639024698455</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>56.59135055541992</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>283.7093505859375</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>7.914594594594595</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>20.39044189453125</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>17.34563064575195</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>18.13009262084961</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>30</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>1.746940062749424</v>
       </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
       <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>11</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>5</v>
       </c>
-      <c r="AB32" t="b">
+      <c r="AC32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3374,79 +3472,82 @@
       <c r="C33" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>10</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>20</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>107.3026456307283</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>11.68854018565822</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>0.07737590094050864</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1.263225173950195</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>103.711050769309</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>11.43323869096514</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>6.782566986912284</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>1386.770872150868</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>1779.306541315042</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>213.1103374070802</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>49.57143020629883</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>232.7940521240234</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>16.55573905862923</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>12.63225173950195</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>10</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>11.36629867553711</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>30</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>1.095209105475656</v>
       </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
       <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>11</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>5</v>
       </c>
-      <c r="AB33" t="b">
+      <c r="AC33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3464,79 +3565,82 @@
       <c r="C34" t="n">
         <v>3</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
         <v>14</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>17</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>84.60826087105715</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>10.37914175412874</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>0.1015448931183933</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>1.822310435489361</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>80.12823388485802</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>9.905138147108945</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>9.260609566329695</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>833.2103986008497</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>819.0545865330657</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>1411.189034707782</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>55.38333511352539</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>158.4251403808594</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>9.623611111111112</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>28.54983139038086</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>15.66683197021484</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>17.05040740966797</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>30</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>1.642906101643113</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
       <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>11</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>5</v>
       </c>
-      <c r="AB34" t="b">
+      <c r="AC34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3554,79 +3658,82 @@
       <c r="C35" t="n">
         <v>4</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>18</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>70.98607444186055</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>9.506959403767899</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>0.08148601149572611</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>1.293207989826299</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>50.12392415733655</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>13.03922259406887</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>7.40082135952594</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>871.1442999708451</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>1083.206262115148</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1224.639024698455</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>62.05330276489258</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>202.5839385986328</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>9.192352259559675</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>22.79791641235352</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>17.62896347045898</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>18.13053894042969</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>30</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>1.746983068241537</v>
       </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
       <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>11</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>5</v>
       </c>
-      <c r="AB35" t="b">
+      <c r="AC35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3644,79 +3751,82 @@
       <c r="C36" t="n">
         <v>5</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
         <v>6</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>18</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>54.88478787165095</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>8.359514478878951</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.05253207905084546</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>1.686667825597837</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>45.71358096794808</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>10.79781865809209</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>8.617657225677537</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>1044.786135696787</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>1248.649246806911</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>1224.639024698455</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>61.12609481811523</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>167.5503540039062</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>8.455341506129598</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>29.05429840087891</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>17.22585678100586</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>18.14437103271484</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>30</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>1.748315870928756</v>
       </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
       <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>11</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>5</v>
       </c>
-      <c r="AB36" t="b">
+      <c r="AC36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3734,79 +3844,82 @@
       <c r="C37" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
         <v>6</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>17</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>34.79319733138874</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>6.655830130802474</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.03330174103830782</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>1.79652994313133</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>33.46178298838706</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>7.402556784500822</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>6.31064822406022</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>1044.786135696787</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>1248.649246806911</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>1411.189034707782</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>72.50373840332031</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>167.5503540039062</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>4.062344139650873</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>29.45373916625977</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>16.39479446411133</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>17.05040740966797</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>30</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.642906101643113</v>
       </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
       <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>11</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>5</v>
       </c>
-      <c r="AB37" t="b">
+      <c r="AC37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3824,79 +3937,82 @@
       <c r="C38" t="n">
         <v>7</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>15</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>5.849635337710113</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>2.729100041085476</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.004725459810385082</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>3.880876674377442</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>2.012310229912006</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6.852833546452089</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2.303504015138129</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>1237.897595669832</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>1507.19069075254</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>217.54359737155</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>63.86956405639648</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>115.2356643676758</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>3.717391304347826</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>32.70329666137695</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>8.426780700683594</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>9.153240203857422</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>30</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>0.8819680268868867</v>
       </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
       <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>11</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>5</v>
       </c>
-      <c r="AB38" t="b">
+      <c r="AC38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3914,79 +4030,82 @@
       <c r="C39" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>16</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>39.61973660261321</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>7.10249360397025</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.03982109116081892</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>0.8187250606368829</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>35.91901761682366</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>9.303492970272256</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>4.373488034459501</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>994.943519819873</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>1366.071787281762</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>1028.084755477271</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>75.52462768554688</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>371.948974609375</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>5.884236453201971</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9.899532318115234</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>12.09140014648438</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>11.94642639160156</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>31</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>1.151107791152465</v>
       </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
       <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>16</v>
       </c>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB39" t="b">
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4004,79 +4123,82 @@
       <c r="C40" t="n">
         <v>2</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
         <v>5</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>16</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>26.94105684664718</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>5.856826696608771</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>0.03443994429079371</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>1.614162974860437</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>18.19012881466651</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8.7432852449531</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>4.866158139926085</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>782.2619171265301</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>860.1701302743434</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>1028.084755477271</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>56.62136077880859</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>213.0353240966797</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>5.135922330097087</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>18.61648178100586</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>11.53321075439453</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>11.89191818237305</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>31</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.145855607589955</v>
       </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
       <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>16</v>
       </c>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB40" t="b">
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4094,79 +4216,82 @@
       <c r="C41" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
         <v>11</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>12</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>43.54597794064011</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>7.446103754863215</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>0.07202459982808872</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>1.749091991714451</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>45.69622759003278</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>8.436038129159021</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>5.523639534758232</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>604.5986794036683</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>659.9280164809455</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>1191.173796825068</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>53.22739791870117</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>382.9418029785156</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>8.531506849315068</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>23.71091079711914</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>13.55612564086914</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>14.23376846313477</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>29</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>1.371506527415863</v>
       </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
       <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>16</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>2</v>
       </c>
-      <c r="AB41" t="b">
+      <c r="AC41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4184,79 +4309,82 @@
       <c r="C42" t="n">
         <v>1</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
         <v>11</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>12</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>20.31670423759613</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>5.08606245085487</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.01335673723064036</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>0.454613598426033</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>20.23299474468698</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>4.744585803663202</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>3.972680703054632</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>1521.082872768478</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>2424.247785172735</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>42.68483930392181</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>80.46111297607422</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>248.7073211669922</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>3.15</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>5.536376953125</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>12.17820358276367</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>9.916950225830078</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>28</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>1.114815294468783</v>
       </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
       <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>16</v>
       </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="b">
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4274,79 +4402,82 @@
       <c r="C43" t="n">
         <v>1</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
         <v>7</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>20</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>191.7018892014548</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>15.6231375252134</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.1791931245776498</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>1.319870030007366</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>195.2420443637932</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>15.5637945658066</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>11.79307234343712</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>1069.806052287372</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>1261.399773253395</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>991.8732603692565</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>85.65777587890625</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>382.922607421875</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>5.450116009280743</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>20.86791229248047</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>15.81058120727539</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>16.97013854980469</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>27</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>1.907700409275072</v>
       </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
       <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>20</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>8</v>
       </c>
-      <c r="AB43" t="b">
+      <c r="AC43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4364,79 +4495,82 @@
       <c r="C44" t="n">
         <v>2</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
         <v>22</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>25</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>63.84750006743872</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>9.016272063238993</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>0.0512157028100285</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>0.8706627243239781</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>57.96537894750909</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>11.0397205698286</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>8.922291093832561</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>1246.6391470652</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>1207.06291439684</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>873.2345158333562</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>62.89115524291992</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>140.3150024414062</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>6.031292517006802</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>14.10186386108398</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>16.19670104980469</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>15.95381164550781</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>27</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>1.793449883529852</v>
       </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
       <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>20</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>8</v>
       </c>
-      <c r="AB44" t="b">
+      <c r="AC44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4454,79 +4588,82 @@
       <c r="C45" t="n">
         <v>3</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
         <v>26</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>25</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>44.7169129072058</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>7.545551128442019</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>0.0530067914210163</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>0.9948678727591906</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>44.04273805548605</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>10.13660723658315</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>6.705652783707531</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>843.6072380241505</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>1055.58666021261</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>873.2345158333562</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>54.03067398071289</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>199.688720703125</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>7.288343558282208</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>15.87891387939453</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>15.9608268737793</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>15.953857421875</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>27</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>1.793455029486331</v>
       </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
       <c r="Y45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>20</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>8</v>
       </c>
-      <c r="AB45" t="b">
+      <c r="AC45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4544,79 +4681,82 @@
       <c r="C46" t="n">
         <v>4</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
         <v>31</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>29</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>42.18874107495716</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>7.329145480833909</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>0.0444072346769803</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>2.063284211666092</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>40.00093001435103</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>7.258418084347448</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>6.720557421751721</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>950.0420681863994</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>1529.906244021815</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>1178.580199934848</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>95.55585479736328</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>81.48159027099609</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>6.572207084468665</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>13.375</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>6.482383728027344</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>6.947479248046875</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>27</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.7810018148073182</v>
       </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
       <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>20</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>8</v>
       </c>
-      <c r="AB46" t="b">
+      <c r="AC46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4634,79 +4774,82 @@
       <c r="C47" t="n">
         <v>5</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
         <v>22</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>20</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>37.65951740896895</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>6.924564015210024</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.03020883589098404</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>1.729052710676868</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>28.95109600971556</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>9.415038539111737</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>9.403787349718531</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>1246.6391470652</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>1207.06291439684</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>991.8732603692565</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>67.49407958984375</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>140.3150024414062</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>5.14792899408284</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>28.15879058837891</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>16.28567504882812</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>16.96840286254883</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>27</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>1.907505291758579</v>
       </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
       <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>20</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>8</v>
       </c>
-      <c r="AB47" t="b">
+      <c r="AC47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4724,79 +4867,82 @@
       <c r="C48" t="n">
         <v>6</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
         <v>27</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>25</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>18.33543860404358</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4.831708341853012</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>0.079058844163036</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>1.203473113403255</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>17.81690223657325</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6.064655033865932</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>3.650683724388564</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>231.9214099087009</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>126.9167786288484</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>873.2345158333562</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>49.04026794433594</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>202.6515655517578</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>9.63758389261745</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>19.03179168701172</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>15.81405639648438</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>15.92612075805664</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>27</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>1.790337008689805</v>
       </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
       <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>20</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>8</v>
       </c>
-      <c r="AB48" t="b">
+      <c r="AC48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4814,79 +4960,82 @@
       <c r="C49" t="n">
         <v>7</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
         <v>7</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>25</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>12.96274146830324</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>4.062594619897736</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.01211690795783718</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>1.23681502992519</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>11.04705230605245</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>9.272378767530702</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>1.784445470901258</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>1069.806052287372</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>1261.399773253395</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>873.2345158333562</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>105.0299987792969</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>382.922607421875</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>5.26</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>19.58560180664062</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>15.83551406860352</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>15.95330810546875</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>27</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>1.793393278008584</v>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>20</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>8</v>
       </c>
-      <c r="AB49" t="b">
+      <c r="AC49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4904,79 +5053,82 @@
       <c r="C50" t="n">
         <v>8</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
         <v>24</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>20</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>2.85732303769013</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>1.907369047580953</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>0.02887294462951255</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>0.578733843026882</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.7100024657034401</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>2.186725428497687</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>1.36933897928384</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>98.96195467259375</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>27.93346101506648</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>991.8732603692565</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>124.529411315918</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>419.0769348144531</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>5.352941176470588</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>9.847328186035156</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>17.01529693603516</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>16.97539901733398</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>27</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>1.908291765440442</v>
       </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
       <c r="Y50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>20</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>8</v>
       </c>
-      <c r="AB50" t="b">
+      <c r="AC50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4994,79 +5146,82 @@
       <c r="C51" t="n">
         <v>1</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
         <v>14</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>9</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>69.20216447183583</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>9.386742373518521</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>0.07607741432415248</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>0.7900956747275985</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>68.46786923647588</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>10.55774251794342</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>8.108088110730542</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>909.6282396898714</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>1376.742997107743</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>1200.746499757197</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>57.98098754882812</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>226.8989715576172</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>6.835234474017744</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>43.94636535644531</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>55.62157440185547</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>54.34227752685547</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>27</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>6.108894442710066</v>
       </c>
-      <c r="X51" t="n">
-        <v>1</v>
-      </c>
       <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>12</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>7</v>
       </c>
-      <c r="AB51" t="b">
+      <c r="AC51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5084,79 +5239,82 @@
       <c r="C52" t="n">
         <v>2</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
         <v>13</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>17</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>61.18569229561592</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>8.826326699299985</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>0.108414990679129</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>1.374906561918302</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>64.82498624709849</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>9.671016860040778</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>8.688621115097899</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>564.3656095189313</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>688.9992167789289</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>1069.631855498276</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>72.80867767333984</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>233.2991180419922</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>7.055226824457594</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>21.47043228149414</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>15.61592102050781</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>16.19664001464844</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>27</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.820747467331753</v>
       </c>
-      <c r="X52" t="n">
-        <v>1</v>
-      </c>
       <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>12</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>7</v>
       </c>
-      <c r="AB52" t="b">
+      <c r="AC52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5174,79 +5332,82 @@
       <c r="C53" t="n">
         <v>3</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
         <v>5</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>17</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>51.48332232385754</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>8.096332618975213</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.07516933218822384</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>1.382210806497017</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>46.74022424476337</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>10.12527966041368</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>7.260491839090461</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>684.8979607127999</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>735.9996188801223</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>1069.631855498276</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>65.58424377441406</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>195.0476684570312</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>5.135667396061269</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>21.55858993530273</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>15.5971794128418</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>16.19669342041016</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>27</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.820753470947645</v>
       </c>
-      <c r="X53" t="n">
-        <v>1</v>
-      </c>
       <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>12</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>7</v>
       </c>
-      <c r="AB53" t="b">
+      <c r="AC53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5264,79 +5425,82 @@
       <c r="C54" t="n">
         <v>4</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
         <v>20</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>9</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>39.1195777863611</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>7.057520344351704</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>0.07108994774088356</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>0.9322188025795687</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>36.79064106863132</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>8.840774817367098</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>5.671762440068829</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>550.2828322359784</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>686.8806677693593</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>1200.746499757197</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>79.11206817626953</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>142.9230346679688</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>4.830459770114943</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>50.87718963623047</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>54.57644653320312</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>54.34227752685547</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>27</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>6.108894442710066</v>
       </c>
-      <c r="X54" t="n">
-        <v>1</v>
-      </c>
       <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>12</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>7</v>
       </c>
-      <c r="AB54" t="b">
+      <c r="AC54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5354,79 +5518,82 @@
       <c r="C55" t="n">
         <v>1</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
         <v>8</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>14</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>161.3021873172543</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>14.33095682585803</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>0.1575366737432416</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>1.29758281022131</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>167.3472753636751</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>14.58396893756067</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>11.86991122183367</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>1023.902457025022</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>1319.071385180569</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>960.7227434507695</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>82.21251678466797</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>378.6636047363281</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>5.999532928538066</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>18.13150024414062</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>13.97328948974609</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>14.97057342529297</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>30</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>1.442501978666151</v>
       </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
       <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>21</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>6</v>
       </c>
-      <c r="AB55" t="b">
+      <c r="AC55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5444,79 +5611,82 @@
       <c r="C56" t="n">
         <v>2</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
         <v>24</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>18</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>95.50236520524766</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>11.02712056681438</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>0.06882390132614877</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>1.041021374008428</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>78.38602474517323</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>11.87045935674072</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>10.23217610367177</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>1387.633705225059</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>1366.267949227093</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>722.8960009320434</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>67.45973205566406</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>151.3825378417969</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>5.915837104072398</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>16.70909118652344</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>16.0506706237793</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>16.17555999755859</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>30</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>1.558609456007173</v>
       </c>
-      <c r="X56" t="n">
-        <v>1</v>
-      </c>
       <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>21</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>6</v>
       </c>
-      <c r="AB56" t="b">
+      <c r="AC56" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5534,79 +5704,82 @@
       <c r="C57" t="n">
         <v>3</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
         <v>26</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>25</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>44.23710646893255</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>7.504960579570328</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>0.04789549974336052</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>1.04316809888089</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>43.80161452731908</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>8.341678666274161</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>6.116589750012188</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>923.6171812794349</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>1462.308837660917</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>1270.148596015136</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>118.0050659179688</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>84.08098602294922</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>7.141772151898734</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>5.820903778076172</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>5.580024719238281</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>5.596988677978516</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>30</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.5393024711341715</v>
       </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
       <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>21</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>6</v>
       </c>
-      <c r="AB57" t="b">
+      <c r="AC57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5624,79 +5797,82 @@
       <c r="C58" t="n">
         <v>4</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
         <v>24</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>14</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>28.69487126960873</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>6.044455710115736</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.02067899558908072</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>1.677204422420961</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>28.69938606133417</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>10.54850864160926</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>5.447419924509113</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>1387.633705225059</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>1366.267949227093</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>960.7227434507695</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>63.78455352783203</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>151.3825378417969</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>4.796747967479675</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>24.12905883789062</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>14.386474609375</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>14.97392272949219</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>30</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>1.442824703641159</v>
       </c>
-      <c r="X58" t="n">
-        <v>1</v>
-      </c>
       <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>21</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
         <v>6</v>
       </c>
-      <c r="AB58" t="b">
+      <c r="AC58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5714,79 +5890,82 @@
       <c r="C59" t="n">
         <v>5</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
         <v>6</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>28</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>28.08281634949455</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>5.979644830900212</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>0.03372199043970103</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>2.609492680108303</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>27.16081199540273</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>8.328191936372214</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>3.272904793903614</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>832.7745777554263</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>1228.523031215999</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>306.6795853297397</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>73.40171051025391</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>476.6447143554688</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>9.33048433048433</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>14.81626510620117</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>5.677833557128906</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>6.881149291992188</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>30</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.6630388287215303</v>
       </c>
-      <c r="X59" t="n">
-        <v>1</v>
-      </c>
       <c r="Y59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>21</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
         <v>6</v>
       </c>
-      <c r="AB59" t="b">
+      <c r="AC59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5804,79 +5983,82 @@
       <c r="C60" t="n">
         <v>6</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
         <v>21</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>18</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>27.47165958082578</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>5.914220433650573</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>0.03834655752598065</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>1.526144806288355</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>25.50437496566868</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>9.303180074604064</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>4.923677162534643</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>716.4048444821444</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>907.4843914880655</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>722.8960009320434</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>51.26511764526367</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>192.9559326171875</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>7.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>23.83240127563477</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>15.61608123779297</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>16.19084167480469</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>30</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>1.560081934651685</v>
       </c>
-      <c r="X60" t="n">
-        <v>1</v>
-      </c>
       <c r="Y60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>21</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
         <v>6</v>
       </c>
-      <c r="AB60" t="b">
+      <c r="AC60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5894,79 +6076,82 @@
       <c r="C61" t="n">
         <v>7</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
         <v>8</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>18</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>4.778121649761839</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>2.466514430128473</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>0.004666578947026663</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>1.41228867138329</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>3.961433531746032</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>2.367708189432491</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>1.498564076360232</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>1023.902457025022</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>1319.071385180569</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>722.8960009320434</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>82.72972869873047</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>378.6636047363281</v>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="n">
         <v>3.027027027027027</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>22.73488235473633</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>16.097900390625</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>16.19084167480469</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>30</v>
       </c>
-      <c r="W61" t="n">
+      <c r="X61" t="n">
         <v>1.560081934651685</v>
       </c>
-      <c r="X61" t="n">
-        <v>1</v>
-      </c>
       <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
         <v>0.1980716765873016</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AA61" t="n">
         <v>21</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
         <v>6</v>
       </c>
-      <c r="AB61" t="b">
+      <c r="AC61" t="b">
         <v>1</v>
       </c>
     </row>
